--- a/crypto_compare/output/l1_comparison.xlsx
+++ b/crypto_compare/output/l1_comparison.xlsx
@@ -279,7 +279,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -414,9 +414,6 @@
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="165" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -489,8 +486,8 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -641,6 +638,12 @@
 комиссии за 365 дн (Ethereum)</t>
       </text>
     </comment>
+    <comment ref="J5" authorId="0" shapeId="0">
+      <text>
+        <t>Open Dev Data, 30.09.2026
+exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+      </text>
+    </comment>
     <comment ref="C6" authorId="0" shapeId="0">
       <text>
         <t>CoinGecko, 30.09.2026</t>
@@ -681,6 +684,12 @@
 комиссии за 365 дн (Solana)</t>
       </text>
     </comment>
+    <comment ref="J6" authorId="0" shapeId="0">
+      <text>
+        <t>Open Dev Data, 30.09.2026
+exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+      </text>
+    </comment>
     <comment ref="C7" authorId="0" shapeId="0">
       <text>
         <t>CoinGecko, 30.09.2026</t>
@@ -721,6 +730,12 @@
 комиссии за 365 дн (Sui)</t>
       </text>
     </comment>
+    <comment ref="J7" authorId="0" shapeId="0">
+      <text>
+        <t>Open Dev Data, 30.09.2026
+exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+      </text>
+    </comment>
     <comment ref="C8" authorId="0" shapeId="0">
       <text>
         <t>CoinGecko, 30.09.2026</t>
@@ -761,6 +776,12 @@
 комиссии за 365 дн (Aptos)</t>
       </text>
     </comment>
+    <comment ref="J8" authorId="0" shapeId="0">
+      <text>
+        <t>Open Dev Data, 30.09.2026
+exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+      </text>
+    </comment>
     <comment ref="C9" authorId="0" shapeId="0">
       <text>
         <t>CoinGecko, 30.09.2026</t>
@@ -801,6 +822,12 @@
 комиссии за 365 дн (Avalanche)</t>
       </text>
     </comment>
+    <comment ref="J9" authorId="0" shapeId="0">
+      <text>
+        <t>Open Dev Data, 30.09.2026
+exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+      </text>
+    </comment>
     <comment ref="C10" authorId="0" shapeId="0">
       <text>
         <t>CoinGecko, 30.09.2026</t>
@@ -841,6 +868,12 @@
 комиссии за 365 дн (Near)</t>
       </text>
     </comment>
+    <comment ref="J10" authorId="0" shapeId="0">
+      <text>
+        <t>Open Dev Data, 30.09.2026
+exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+      </text>
+    </comment>
     <comment ref="C11" authorId="0" shapeId="0">
       <text>
         <t>CoinGecko, 30.09.2026</t>
@@ -881,6 +914,12 @@
 комиссии за 365 дн (TON)</t>
       </text>
     </comment>
+    <comment ref="J11" authorId="0" shapeId="0">
+      <text>
+        <t>Open Dev Data, 30.09.2026
+exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+      </text>
+    </comment>
     <comment ref="C12" authorId="0" shapeId="0">
       <text>
         <t>CoinGecko, 30.09.2026</t>
@@ -921,6 +960,12 @@
 комиссии за 365 дн (Tron)</t>
       </text>
     </comment>
+    <comment ref="J12" authorId="0" shapeId="0">
+      <text>
+        <t>Open Dev Data, 30.09.2026
+exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+      </text>
+    </comment>
     <comment ref="C13" authorId="0" shapeId="0">
       <text>
         <t>CoinGecko, 30.09.2026</t>
@@ -961,6 +1006,12 @@
 комиссии за 365 дн (Hyperliquid)</t>
       </text>
     </comment>
+    <comment ref="J13" authorId="0" shapeId="0">
+      <text>
+        <t>Open Dev Data, 30.09.2026
+exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0. ⚠ за 6 мес 24 → 4: скачок больше чем в 5 раз, часто это перепривязка общих репозиториев к сети, а не реальный приток разработчиков</t>
+      </text>
+    </comment>
     <comment ref="C14" authorId="0" shapeId="0">
       <text>
         <t>CoinGecko, 30.09.2026</t>
@@ -999,6 +1050,12 @@
       <text>
         <t>DeFiLlama, 30.09.2026
 комиссии за 365 дн (Monad)</t>
+      </text>
+    </comment>
+    <comment ref="J14" authorId="0" shapeId="0">
+      <text>
+        <t>Open Dev Data, 30.09.2026
+exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
       </text>
     </comment>
   </commentList>
@@ -1397,13 +1454,13 @@
         </is>
       </c>
       <c r="C5" s="44" t="n">
-        <v>327258.690254</v>
+        <v>327944.680337</v>
       </c>
       <c r="D5" s="44" t="n">
-        <v>327258.690254</v>
+        <v>327944.680337</v>
       </c>
       <c r="E5" s="44" t="n">
-        <v>53918.369868</v>
+        <v>53303.04256</v>
       </c>
       <c r="F5" s="44" t="n">
         <v>53909.531522</v>
@@ -1417,34 +1474,36 @@
       <c r="I5" s="45" t="n">
         <v>202.689948</v>
       </c>
-      <c r="J5" s="46" t="n"/>
-      <c r="K5" s="47" t="n"/>
-      <c r="L5" s="48" t="n"/>
-      <c r="M5" s="49">
+      <c r="J5" s="44" t="n">
+        <v>3270</v>
+      </c>
+      <c r="K5" s="46" t="n"/>
+      <c r="L5" s="47" t="n"/>
+      <c r="M5" s="48">
         <f>IF(OR(E5="",F5="",F5=0),"",E5/F5-1)</f>
         <v/>
       </c>
-      <c r="N5" s="49">
+      <c r="N5" s="48">
         <f>IF(OR(G5="",H5="",H5=0),"",G5/H5-1)</f>
         <v/>
       </c>
-      <c r="O5" s="50">
+      <c r="O5" s="49">
         <f>IF(OR(C5="",E5="",E5=0),"",C5/E5)</f>
         <v/>
       </c>
-      <c r="P5" s="51">
+      <c r="P5" s="50">
         <f>IF(OR(C5="",I5="",I5=0),"",C5/I5)</f>
         <v/>
       </c>
-      <c r="Q5" s="50">
+      <c r="Q5" s="49">
         <f>IF(OR(C5="",D5="",C5=0),"",D5/C5)</f>
         <v/>
       </c>
-      <c r="R5" s="52">
+      <c r="R5" s="51">
         <f>Расчёт!K5</f>
         <v/>
       </c>
-      <c r="S5" s="52">
+      <c r="S5" s="51">
         <f>IF(R5="","",RANK(R5,$R$5:$R$14))</f>
         <v/>
       </c>
@@ -1461,13 +1520,13 @@
         </is>
       </c>
       <c r="C6" s="44" t="n">
-        <v>69988.26169699999</v>
+        <v>70355.204557</v>
       </c>
       <c r="D6" s="44" t="n">
-        <v>75581.369252</v>
+        <v>75977.633946</v>
       </c>
       <c r="E6" s="44" t="n">
-        <v>6471.36886</v>
+        <v>6568.178533</v>
       </c>
       <c r="F6" s="44" t="n">
         <v>6357.767767</v>
@@ -1481,34 +1540,36 @@
       <c r="I6" s="45" t="n">
         <v>239.426752</v>
       </c>
-      <c r="J6" s="46" t="n"/>
-      <c r="K6" s="47" t="n"/>
-      <c r="L6" s="48" t="n"/>
-      <c r="M6" s="49">
+      <c r="J6" s="44" t="n">
+        <v>1080</v>
+      </c>
+      <c r="K6" s="46" t="n"/>
+      <c r="L6" s="47" t="n"/>
+      <c r="M6" s="48">
         <f>IF(OR(E6="",F6="",F6=0),"",E6/F6-1)</f>
         <v/>
       </c>
-      <c r="N6" s="49">
+      <c r="N6" s="48">
         <f>IF(OR(G6="",H6="",H6=0),"",G6/H6-1)</f>
         <v/>
       </c>
-      <c r="O6" s="50">
+      <c r="O6" s="49">
         <f>IF(OR(C6="",E6="",E6=0),"",C6/E6)</f>
         <v/>
       </c>
-      <c r="P6" s="51">
+      <c r="P6" s="50">
         <f>IF(OR(C6="",I6="",I6=0),"",C6/I6)</f>
         <v/>
       </c>
-      <c r="Q6" s="50">
+      <c r="Q6" s="49">
         <f>IF(OR(C6="",D6="",C6=0),"",D6/C6)</f>
         <v/>
       </c>
-      <c r="R6" s="52">
+      <c r="R6" s="51">
         <f>Расчёт!K6</f>
         <v/>
       </c>
-      <c r="S6" s="52">
+      <c r="S6" s="51">
         <f>IF(R6="","",RANK(R6,$R$5:$R$14))</f>
         <v/>
       </c>
@@ -1525,13 +1586,13 @@
         </is>
       </c>
       <c r="C7" s="44" t="n">
-        <v>4767.521283</v>
+        <v>4865.721245</v>
       </c>
       <c r="D7" s="44" t="n">
-        <v>11637.930067</v>
+        <v>11877.644633</v>
       </c>
       <c r="E7" s="44" t="n">
-        <v>559.329125</v>
+        <v>551.750347</v>
       </c>
       <c r="F7" s="44" t="n">
         <v>570.720387</v>
@@ -1545,34 +1606,36 @@
       <c r="I7" s="45" t="n">
         <v>3.512066</v>
       </c>
-      <c r="J7" s="46" t="n"/>
-      <c r="K7" s="47" t="n"/>
-      <c r="L7" s="48" t="n"/>
-      <c r="M7" s="49">
+      <c r="J7" s="44" t="n">
+        <v>254</v>
+      </c>
+      <c r="K7" s="46" t="n"/>
+      <c r="L7" s="47" t="n"/>
+      <c r="M7" s="48">
         <f>IF(OR(E7="",F7="",F7=0),"",E7/F7-1)</f>
         <v/>
       </c>
-      <c r="N7" s="49">
+      <c r="N7" s="48">
         <f>IF(OR(G7="",H7="",H7=0),"",G7/H7-1)</f>
         <v/>
       </c>
-      <c r="O7" s="50">
+      <c r="O7" s="49">
         <f>IF(OR(C7="",E7="",E7=0),"",C7/E7)</f>
         <v/>
       </c>
-      <c r="P7" s="51">
+      <c r="P7" s="50">
         <f>IF(OR(C7="",I7="",I7=0),"",C7/I7)</f>
         <v/>
       </c>
-      <c r="Q7" s="50">
+      <c r="Q7" s="49">
         <f>IF(OR(C7="",D7="",C7=0),"",D7/C7)</f>
         <v/>
       </c>
-      <c r="R7" s="52">
+      <c r="R7" s="51">
         <f>Расчёт!K7</f>
         <v/>
       </c>
-      <c r="S7" s="52">
+      <c r="S7" s="51">
         <f>IF(R7="","",RANK(R7,$R$5:$R$14))</f>
         <v/>
       </c>
@@ -1589,18 +1652,18 @@
         </is>
       </c>
       <c r="C8" s="44" t="n">
-        <v>687.9191049999999</v>
+        <v>690.49137</v>
       </c>
       <c r="D8" s="44" t="n">
-        <v>955.210046</v>
+        <v>958.7853270000001</v>
       </c>
       <c r="E8" s="44" t="n">
-        <v>55.740282</v>
+        <v>55.53995</v>
       </c>
       <c r="F8" s="44" t="n">
         <v>285.748159</v>
       </c>
-      <c r="G8" s="53" t="n">
+      <c r="G8" s="52" t="n">
         <v>35921</v>
       </c>
       <c r="H8" s="44" t="n">
@@ -1609,34 +1672,36 @@
       <c r="I8" s="45" t="n">
         <v>1.145126</v>
       </c>
-      <c r="J8" s="46" t="n"/>
-      <c r="K8" s="47" t="n"/>
-      <c r="L8" s="48" t="n"/>
-      <c r="M8" s="49">
+      <c r="J8" s="44" t="n">
+        <v>92</v>
+      </c>
+      <c r="K8" s="46" t="n"/>
+      <c r="L8" s="47" t="n"/>
+      <c r="M8" s="48">
         <f>IF(OR(E8="",F8="",F8=0),"",E8/F8-1)</f>
         <v/>
       </c>
-      <c r="N8" s="49">
+      <c r="N8" s="48">
         <f>IF(OR(G8="",H8="",H8=0),"",G8/H8-1)</f>
         <v/>
       </c>
-      <c r="O8" s="50">
+      <c r="O8" s="49">
         <f>IF(OR(C8="",E8="",E8=0),"",C8/E8)</f>
         <v/>
       </c>
-      <c r="P8" s="51">
+      <c r="P8" s="50">
         <f>IF(OR(C8="",I8="",I8=0),"",C8/I8)</f>
         <v/>
       </c>
-      <c r="Q8" s="50">
+      <c r="Q8" s="49">
         <f>IF(OR(C8="",D8="",C8=0),"",D8/C8)</f>
         <v/>
       </c>
-      <c r="R8" s="52">
+      <c r="R8" s="51">
         <f>Расчёт!K8</f>
         <v/>
       </c>
-      <c r="S8" s="52">
+      <c r="S8" s="51">
         <f>IF(R8="","",RANK(R8,$R$5:$R$14))</f>
         <v/>
       </c>
@@ -1653,54 +1718,56 @@
         </is>
       </c>
       <c r="C9" s="44" t="n">
-        <v>4829.34046</v>
+        <v>4879.641119</v>
       </c>
       <c r="D9" s="44" t="n">
-        <v>5120.001442</v>
+        <v>5173.313795</v>
       </c>
       <c r="E9" s="44" t="n">
-        <v>640.767554</v>
+        <v>626.279733</v>
       </c>
       <c r="F9" s="44" t="n">
         <v>724.301796</v>
       </c>
-      <c r="G9" s="53" t="n">
+      <c r="G9" s="52" t="n">
         <v>21091</v>
       </c>
-      <c r="H9" s="53" t="n">
+      <c r="H9" s="52" t="n">
         <v>643627</v>
       </c>
       <c r="I9" s="45" t="n">
         <v>4.076565</v>
       </c>
-      <c r="J9" s="46" t="n"/>
-      <c r="K9" s="47" t="n"/>
-      <c r="L9" s="48" t="n"/>
-      <c r="M9" s="49">
+      <c r="J9" s="44" t="n">
+        <v>108</v>
+      </c>
+      <c r="K9" s="46" t="n"/>
+      <c r="L9" s="47" t="n"/>
+      <c r="M9" s="48">
         <f>IF(OR(E9="",F9="",F9=0),"",E9/F9-1)</f>
         <v/>
       </c>
-      <c r="N9" s="49">
+      <c r="N9" s="48">
         <f>IF(OR(G9="",H9="",H9=0),"",G9/H9-1)</f>
         <v/>
       </c>
-      <c r="O9" s="50">
+      <c r="O9" s="49">
         <f>IF(OR(C9="",E9="",E9=0),"",C9/E9)</f>
         <v/>
       </c>
-      <c r="P9" s="51">
+      <c r="P9" s="50">
         <f>IF(OR(C9="",I9="",I9=0),"",C9/I9)</f>
         <v/>
       </c>
-      <c r="Q9" s="50">
+      <c r="Q9" s="49">
         <f>IF(OR(C9="",D9="",C9=0),"",D9/C9)</f>
         <v/>
       </c>
-      <c r="R9" s="52">
+      <c r="R9" s="51">
         <f>Расчёт!K9</f>
         <v/>
       </c>
-      <c r="S9" s="52">
+      <c r="S9" s="51">
         <f>IF(R9="","",RANK(R9,$R$5:$R$14))</f>
         <v/>
       </c>
@@ -1717,54 +1784,56 @@
         </is>
       </c>
       <c r="C10" s="44" t="n">
-        <v>6908.777867</v>
+        <v>7048.836656</v>
       </c>
       <c r="D10" s="44" t="n">
-        <v>6908.778987</v>
+        <v>7048.837611</v>
       </c>
       <c r="E10" s="44" t="n">
-        <v>239.929727</v>
+        <v>236.616937</v>
       </c>
       <c r="F10" s="44" t="n">
         <v>95.21909100000001</v>
       </c>
-      <c r="G10" s="53" t="n">
+      <c r="G10" s="52" t="n">
         <v>76790</v>
       </c>
-      <c r="H10" s="53" t="n">
+      <c r="H10" s="52" t="n">
         <v>3067142</v>
       </c>
       <c r="I10" s="45" t="n">
         <v>1.261909</v>
       </c>
-      <c r="J10" s="46" t="n"/>
-      <c r="K10" s="47" t="n"/>
-      <c r="L10" s="48" t="n"/>
-      <c r="M10" s="49">
+      <c r="J10" s="44" t="n">
+        <v>150</v>
+      </c>
+      <c r="K10" s="46" t="n"/>
+      <c r="L10" s="47" t="n"/>
+      <c r="M10" s="48">
         <f>IF(OR(E10="",F10="",F10=0),"",E10/F10-1)</f>
         <v/>
       </c>
-      <c r="N10" s="49">
+      <c r="N10" s="48">
         <f>IF(OR(G10="",H10="",H10=0),"",G10/H10-1)</f>
         <v/>
       </c>
-      <c r="O10" s="50">
+      <c r="O10" s="49">
         <f>IF(OR(C10="",E10="",E10=0),"",C10/E10)</f>
         <v/>
       </c>
-      <c r="P10" s="51">
+      <c r="P10" s="50">
         <f>IF(OR(C10="",I10="",I10=0),"",C10/I10)</f>
         <v/>
       </c>
-      <c r="Q10" s="50">
+      <c r="Q10" s="49">
         <f>IF(OR(C10="",D10="",C10=0),"",D10/C10)</f>
         <v/>
       </c>
-      <c r="R10" s="52">
+      <c r="R10" s="51">
         <f>Расчёт!K10</f>
         <v/>
       </c>
-      <c r="S10" s="52">
+      <c r="S10" s="51">
         <f>IF(R10="","",RANK(R10,$R$5:$R$14))</f>
         <v/>
       </c>
@@ -1781,13 +1850,13 @@
         </is>
       </c>
       <c r="C11" s="44" t="n">
-        <v>4228.799095</v>
+        <v>4238.049641</v>
       </c>
       <c r="D11" s="44" t="n">
-        <v>7895.284465</v>
+        <v>7912.528129</v>
       </c>
       <c r="E11" s="44" t="n">
-        <v>55.149255</v>
+        <v>54.352401</v>
       </c>
       <c r="F11" s="44" t="n">
         <v>55.174661</v>
@@ -1801,34 +1870,36 @@
       <c r="I11" s="45" t="n">
         <v>2.119862</v>
       </c>
-      <c r="J11" s="46" t="n"/>
-      <c r="K11" s="47" t="n"/>
-      <c r="L11" s="48" t="n"/>
-      <c r="M11" s="49">
+      <c r="J11" s="44" t="n">
+        <v>191</v>
+      </c>
+      <c r="K11" s="46" t="n"/>
+      <c r="L11" s="47" t="n"/>
+      <c r="M11" s="48">
         <f>IF(OR(E11="",F11="",F11=0),"",E11/F11-1)</f>
         <v/>
       </c>
-      <c r="N11" s="49">
+      <c r="N11" s="48">
         <f>IF(OR(G11="",H11="",H11=0),"",G11/H11-1)</f>
         <v/>
       </c>
-      <c r="O11" s="50">
+      <c r="O11" s="49">
         <f>IF(OR(C11="",E11="",E11=0),"",C11/E11)</f>
         <v/>
       </c>
-      <c r="P11" s="51">
+      <c r="P11" s="50">
         <f>IF(OR(C11="",I11="",I11=0),"",C11/I11)</f>
         <v/>
       </c>
-      <c r="Q11" s="50">
+      <c r="Q11" s="49">
         <f>IF(OR(C11="",D11="",C11=0),"",D11/C11)</f>
         <v/>
       </c>
-      <c r="R11" s="52">
+      <c r="R11" s="51">
         <f>Расчёт!K11</f>
         <v/>
       </c>
-      <c r="S11" s="52">
+      <c r="S11" s="51">
         <f>IF(R11="","",RANK(R11,$R$5:$R$14))</f>
         <v/>
       </c>
@@ -1845,13 +1916,13 @@
         </is>
       </c>
       <c r="C12" s="44" t="n">
-        <v>32174.288951</v>
+        <v>32097.231712</v>
       </c>
       <c r="D12" s="44" t="n">
-        <v>32174.313939</v>
+        <v>32097.240025</v>
       </c>
       <c r="E12" s="44" t="n">
-        <v>5678.20312</v>
+        <v>5638.408003</v>
       </c>
       <c r="F12" s="44" t="n">
         <v>4797.537404</v>
@@ -1865,34 +1936,36 @@
       <c r="I12" s="45" t="n">
         <v>348.971536</v>
       </c>
-      <c r="J12" s="46" t="n"/>
-      <c r="K12" s="47" t="n"/>
-      <c r="L12" s="48" t="n"/>
-      <c r="M12" s="49">
+      <c r="J12" s="44" t="n">
+        <v>70</v>
+      </c>
+      <c r="K12" s="46" t="n"/>
+      <c r="L12" s="47" t="n"/>
+      <c r="M12" s="48">
         <f>IF(OR(E12="",F12="",F12=0),"",E12/F12-1)</f>
         <v/>
       </c>
-      <c r="N12" s="49">
+      <c r="N12" s="48">
         <f>IF(OR(G12="",H12="",H12=0),"",G12/H12-1)</f>
         <v/>
       </c>
-      <c r="O12" s="50">
+      <c r="O12" s="49">
         <f>IF(OR(C12="",E12="",E12=0),"",C12/E12)</f>
         <v/>
       </c>
-      <c r="P12" s="51">
+      <c r="P12" s="50">
         <f>IF(OR(C12="",I12="",I12=0),"",C12/I12)</f>
         <v/>
       </c>
-      <c r="Q12" s="50">
+      <c r="Q12" s="49">
         <f>IF(OR(C12="",D12="",C12=0),"",D12/C12)</f>
         <v/>
       </c>
-      <c r="R12" s="52">
+      <c r="R12" s="51">
         <f>Расчёт!K12</f>
         <v/>
       </c>
-      <c r="S12" s="52">
+      <c r="S12" s="51">
         <f>IF(R12="","",RANK(R12,$R$5:$R$14))</f>
         <v/>
       </c>
@@ -1909,13 +1982,13 @@
         </is>
       </c>
       <c r="C13" s="44" t="n">
-        <v>19075.239849</v>
+        <v>19786.883821</v>
       </c>
       <c r="D13" s="44" t="n">
-        <v>81919.814663</v>
+        <v>84976.014364</v>
       </c>
       <c r="E13" s="44" t="n">
-        <v>1190.593415</v>
+        <v>1171.952848</v>
       </c>
       <c r="F13" s="44" t="n">
         <v>1672.171573</v>
@@ -1929,34 +2002,36 @@
       <c r="I13" s="45" t="n">
         <v>910.588444</v>
       </c>
-      <c r="J13" s="46" t="n"/>
-      <c r="K13" s="47" t="n"/>
-      <c r="L13" s="48" t="n"/>
-      <c r="M13" s="49">
+      <c r="J13" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" s="46" t="n"/>
+      <c r="L13" s="47" t="n"/>
+      <c r="M13" s="48">
         <f>IF(OR(E13="",F13="",F13=0),"",E13/F13-1)</f>
         <v/>
       </c>
-      <c r="N13" s="49">
+      <c r="N13" s="48">
         <f>IF(OR(G13="",H13="",H13=0),"",G13/H13-1)</f>
         <v/>
       </c>
-      <c r="O13" s="50">
+      <c r="O13" s="49">
         <f>IF(OR(C13="",E13="",E13=0),"",C13/E13)</f>
         <v/>
       </c>
-      <c r="P13" s="51">
+      <c r="P13" s="50">
         <f>IF(OR(C13="",I13="",I13=0),"",C13/I13)</f>
         <v/>
       </c>
-      <c r="Q13" s="50">
+      <c r="Q13" s="49">
         <f>IF(OR(C13="",D13="",C13=0),"",D13/C13)</f>
         <v/>
       </c>
-      <c r="R13" s="52">
+      <c r="R13" s="51">
         <f>Расчёт!K13</f>
         <v/>
       </c>
-      <c r="S13" s="52">
+      <c r="S13" s="51">
         <f>IF(R13="","",RANK(R13,$R$5:$R$14))</f>
         <v/>
       </c>
@@ -1973,13 +2048,13 @@
         </is>
       </c>
       <c r="C14" s="44" t="n">
-        <v>328.245041</v>
+        <v>331.544745</v>
       </c>
       <c r="D14" s="44" t="n">
-        <v>2794.774601</v>
+        <v>2822.869252</v>
       </c>
       <c r="E14" s="44" t="n">
-        <v>1052.269901</v>
+        <v>1052.427495</v>
       </c>
       <c r="F14" s="44" t="n">
         <v>351.735124</v>
@@ -1993,34 +2068,36 @@
       <c r="I14" s="45" t="n">
         <v>2.102234</v>
       </c>
-      <c r="J14" s="46" t="n"/>
-      <c r="K14" s="47" t="n"/>
-      <c r="L14" s="48" t="n"/>
-      <c r="M14" s="49">
+      <c r="J14" s="44" t="n">
+        <v>75</v>
+      </c>
+      <c r="K14" s="46" t="n"/>
+      <c r="L14" s="47" t="n"/>
+      <c r="M14" s="48">
         <f>IF(OR(E14="",F14="",F14=0),"",E14/F14-1)</f>
         <v/>
       </c>
-      <c r="N14" s="49">
+      <c r="N14" s="48">
         <f>IF(OR(G14="",H14="",H14=0),"",G14/H14-1)</f>
         <v/>
       </c>
-      <c r="O14" s="50">
+      <c r="O14" s="49">
         <f>IF(OR(C14="",E14="",E14=0),"",C14/E14)</f>
         <v/>
       </c>
-      <c r="P14" s="51">
+      <c r="P14" s="50">
         <f>IF(OR(C14="",I14="",I14=0),"",C14/I14)</f>
         <v/>
       </c>
-      <c r="Q14" s="50">
+      <c r="Q14" s="49">
         <f>IF(OR(C14="",D14="",C14=0),"",D14/C14)</f>
         <v/>
       </c>
-      <c r="R14" s="52">
+      <c r="R14" s="51">
         <f>Расчёт!K14</f>
         <v/>
       </c>
-      <c r="S14" s="52">
+      <c r="S14" s="51">
         <f>IF(R14="","",RANK(R14,$R$5:$R$14))</f>
         <v/>
       </c>
@@ -2047,7 +2124,7 @@
       <c r="S15" s="36" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="34">
-      <c r="A16" s="54" t="inlineStr">
+      <c r="A16" s="53" t="inlineStr">
         <is>
           <t>Легенда: зелёный — лучше среди сравниваемых, красный — хуже. Для Mcap/TVL, Mcap/Доход и FDV/Mcap меньше = лучше. Лидер по баллу подсвечен зелёным.</t>
         </is>
@@ -2072,7 +2149,7 @@
       <c r="S16" s="36" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="34">
-      <c r="A17" s="55" t="inlineStr">
+      <c r="A17" s="54" t="inlineStr">
         <is>
           <t>Балл относительный: показывает, кто сильнее внутри твоей выборки, а не «покупать/не покупать». Сравнивай сети одной категории.</t>
         </is>
@@ -2221,7 +2298,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="34">
-      <c r="A1" s="56" t="inlineStr">
+      <c r="A1" s="55" t="inlineStr">
         <is>
           <t>Служебный лист: нормированные оценки 0–1 по каждой метрике</t>
         </is>
@@ -2320,66 +2397,66 @@
       <c r="AA3" s="36" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="34">
-      <c r="A4" s="56" t="inlineStr">
+      <c r="A4" s="55" t="inlineStr">
         <is>
           <t>Экосистема</t>
         </is>
       </c>
-      <c r="B4" s="56" t="inlineStr">
+      <c r="B4" s="55" t="inlineStr">
         <is>
           <t>Рост TVL 6м</t>
         </is>
       </c>
-      <c r="C4" s="56" t="inlineStr">
+      <c r="C4" s="55" t="inlineStr">
         <is>
           <t>Рост адресов 6м</t>
         </is>
       </c>
-      <c r="D4" s="56" t="inlineStr">
+      <c r="D4" s="55" t="inlineStr">
         <is>
           <t>Mcap / TVL</t>
         </is>
       </c>
-      <c r="E4" s="56" t="inlineStr">
+      <c r="E4" s="55" t="inlineStr">
         <is>
           <t>Mcap / Доход</t>
         </is>
       </c>
-      <c r="F4" s="56" t="inlineStr">
+      <c r="F4" s="55" t="inlineStr">
         <is>
           <t>Активных разработчиков</t>
         </is>
       </c>
-      <c r="G4" s="56" t="inlineStr">
+      <c r="G4" s="55" t="inlineStr">
         <is>
           <t>Разлок за 6 мес</t>
         </is>
       </c>
-      <c r="H4" s="56" t="inlineStr">
+      <c r="H4" s="55" t="inlineStr">
         <is>
           <t>FDV / Mcap</t>
         </is>
       </c>
-      <c r="I4" s="56" t="inlineStr">
+      <c r="I4" s="55" t="inlineStr">
         <is>
           <t>Инвесторы и команда</t>
         </is>
       </c>
-      <c r="J4" s="56" t="n"/>
-      <c r="K4" s="56" t="inlineStr">
+      <c r="J4" s="55" t="n"/>
+      <c r="K4" s="55" t="inlineStr">
         <is>
           <t>Итог 0–100</t>
         </is>
       </c>
-      <c r="L4" s="56" t="n"/>
-      <c r="M4" s="56" t="n"/>
-      <c r="N4" s="56" t="n"/>
-      <c r="O4" s="56" t="n"/>
-      <c r="P4" s="56" t="n"/>
-      <c r="Q4" s="56" t="n"/>
-      <c r="R4" s="56" t="n"/>
-      <c r="S4" s="56" t="n"/>
-      <c r="T4" s="56" t="n"/>
+      <c r="L4" s="55" t="n"/>
+      <c r="M4" s="55" t="n"/>
+      <c r="N4" s="55" t="n"/>
+      <c r="O4" s="55" t="n"/>
+      <c r="P4" s="55" t="n"/>
+      <c r="Q4" s="55" t="n"/>
+      <c r="R4" s="55" t="n"/>
+      <c r="S4" s="55" t="n"/>
+      <c r="T4" s="55" t="n"/>
       <c r="U4" s="36" t="n"/>
       <c r="V4" s="36" t="n"/>
       <c r="W4" s="36" t="n"/>
@@ -2393,40 +2470,40 @@
         <f>IF(Сравнение!A5="","",Сравнение!A5)</f>
         <v/>
       </c>
-      <c r="B5" s="57">
+      <c r="B5" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!M5)),COUNT(Сравнение!$M$5:$M$14)&lt;2),"",IF(MAX(Сравнение!$M$5:$M$14)=MIN(Сравнение!$M$5:$M$14),0.5,(Сравнение!M5-MIN(Сравнение!$M$5:$M$14))/(MAX(Сравнение!$M$5:$M$14)-MIN(Сравнение!$M$5:$M$14))))</f>
         <v/>
       </c>
-      <c r="C5" s="57">
+      <c r="C5" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!N5)),COUNT(Сравнение!$N$5:$N$14)&lt;2),"",IF(MAX(Сравнение!$N$5:$N$14)=MIN(Сравнение!$N$5:$N$14),0.5,(Сравнение!N5-MIN(Сравнение!$N$5:$N$14))/(MAX(Сравнение!$N$5:$N$14)-MIN(Сравнение!$N$5:$N$14))))</f>
         <v/>
       </c>
-      <c r="D5" s="57">
+      <c r="D5" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!O5)),COUNT(Сравнение!$O$5:$O$14)&lt;2),"",IF(MAX(Сравнение!$O$5:$O$14)=MIN(Сравнение!$O$5:$O$14),0.5,(MAX(Сравнение!$O$5:$O$14)-Сравнение!O5)/(MAX(Сравнение!$O$5:$O$14)-MIN(Сравнение!$O$5:$O$14))))</f>
         <v/>
       </c>
-      <c r="E5" s="57">
+      <c r="E5" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!P5)),COUNT(Сравнение!$P$5:$P$14)&lt;2),"",IF(MAX(Сравнение!$P$5:$P$14)=MIN(Сравнение!$P$5:$P$14),0.5,(MAX(Сравнение!$P$5:$P$14)-Сравнение!P5)/(MAX(Сравнение!$P$5:$P$14)-MIN(Сравнение!$P$5:$P$14))))</f>
         <v/>
       </c>
-      <c r="F5" s="57">
+      <c r="F5" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!J5)),COUNT(Сравнение!$J$5:$J$14)&lt;2),"",IF(MAX(Сравнение!$J$5:$J$14)=MIN(Сравнение!$J$5:$J$14),0.5,(Сравнение!J5-MIN(Сравнение!$J$5:$J$14))/(MAX(Сравнение!$J$5:$J$14)-MIN(Сравнение!$J$5:$J$14))))</f>
         <v/>
       </c>
-      <c r="G5" s="57">
+      <c r="G5" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!K5)),COUNT(Сравнение!$K$5:$K$14)&lt;2),"",IF(MAX(Сравнение!$K$5:$K$14)=MIN(Сравнение!$K$5:$K$14),0.5,(MAX(Сравнение!$K$5:$K$14)-Сравнение!K5)/(MAX(Сравнение!$K$5:$K$14)-MIN(Сравнение!$K$5:$K$14))))</f>
         <v/>
       </c>
-      <c r="H5" s="57">
+      <c r="H5" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!Q5)),COUNT(Сравнение!$Q$5:$Q$14)&lt;2),"",IF(MAX(Сравнение!$Q$5:$Q$14)=MIN(Сравнение!$Q$5:$Q$14),0.5,(MAX(Сравнение!$Q$5:$Q$14)-Сравнение!Q5)/(MAX(Сравнение!$Q$5:$Q$14)-MIN(Сравнение!$Q$5:$Q$14))))</f>
         <v/>
       </c>
-      <c r="I5" s="57">
+      <c r="I5" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!L5)),COUNT(Сравнение!$L$5:$L$14)&lt;2),"",IF(MAX(Сравнение!$L$5:$L$14)=MIN(Сравнение!$L$5:$L$14),0.5,(Сравнение!L5-MIN(Сравнение!$L$5:$L$14))/(MAX(Сравнение!$L$5:$L$14)-MIN(Сравнение!$L$5:$L$14))))</f>
         <v/>
       </c>
       <c r="J5" s="36" t="n"/>
-      <c r="K5" s="58">
+      <c r="K5" s="57">
         <f>IF(OR(Сравнение!A5="",SUM(T5:AA5)=0),"",100*SUM(L5:S5)/SUM(T5:AA5))</f>
         <v/>
       </c>
@@ -2500,40 +2577,40 @@
         <f>IF(Сравнение!A6="","",Сравнение!A6)</f>
         <v/>
       </c>
-      <c r="B6" s="57">
+      <c r="B6" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!M6)),COUNT(Сравнение!$M$5:$M$14)&lt;2),"",IF(MAX(Сравнение!$M$5:$M$14)=MIN(Сравнение!$M$5:$M$14),0.5,(Сравнение!M6-MIN(Сравнение!$M$5:$M$14))/(MAX(Сравнение!$M$5:$M$14)-MIN(Сравнение!$M$5:$M$14))))</f>
         <v/>
       </c>
-      <c r="C6" s="57">
+      <c r="C6" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!N6)),COUNT(Сравнение!$N$5:$N$14)&lt;2),"",IF(MAX(Сравнение!$N$5:$N$14)=MIN(Сравнение!$N$5:$N$14),0.5,(Сравнение!N6-MIN(Сравнение!$N$5:$N$14))/(MAX(Сравнение!$N$5:$N$14)-MIN(Сравнение!$N$5:$N$14))))</f>
         <v/>
       </c>
-      <c r="D6" s="57">
+      <c r="D6" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!O6)),COUNT(Сравнение!$O$5:$O$14)&lt;2),"",IF(MAX(Сравнение!$O$5:$O$14)=MIN(Сравнение!$O$5:$O$14),0.5,(MAX(Сравнение!$O$5:$O$14)-Сравнение!O6)/(MAX(Сравнение!$O$5:$O$14)-MIN(Сравнение!$O$5:$O$14))))</f>
         <v/>
       </c>
-      <c r="E6" s="57">
+      <c r="E6" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!P6)),COUNT(Сравнение!$P$5:$P$14)&lt;2),"",IF(MAX(Сравнение!$P$5:$P$14)=MIN(Сравнение!$P$5:$P$14),0.5,(MAX(Сравнение!$P$5:$P$14)-Сравнение!P6)/(MAX(Сравнение!$P$5:$P$14)-MIN(Сравнение!$P$5:$P$14))))</f>
         <v/>
       </c>
-      <c r="F6" s="57">
+      <c r="F6" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!J6)),COUNT(Сравнение!$J$5:$J$14)&lt;2),"",IF(MAX(Сравнение!$J$5:$J$14)=MIN(Сравнение!$J$5:$J$14),0.5,(Сравнение!J6-MIN(Сравнение!$J$5:$J$14))/(MAX(Сравнение!$J$5:$J$14)-MIN(Сравнение!$J$5:$J$14))))</f>
         <v/>
       </c>
-      <c r="G6" s="57">
+      <c r="G6" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!K6)),COUNT(Сравнение!$K$5:$K$14)&lt;2),"",IF(MAX(Сравнение!$K$5:$K$14)=MIN(Сравнение!$K$5:$K$14),0.5,(MAX(Сравнение!$K$5:$K$14)-Сравнение!K6)/(MAX(Сравнение!$K$5:$K$14)-MIN(Сравнение!$K$5:$K$14))))</f>
         <v/>
       </c>
-      <c r="H6" s="57">
+      <c r="H6" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!Q6)),COUNT(Сравнение!$Q$5:$Q$14)&lt;2),"",IF(MAX(Сравнение!$Q$5:$Q$14)=MIN(Сравнение!$Q$5:$Q$14),0.5,(MAX(Сравнение!$Q$5:$Q$14)-Сравнение!Q6)/(MAX(Сравнение!$Q$5:$Q$14)-MIN(Сравнение!$Q$5:$Q$14))))</f>
         <v/>
       </c>
-      <c r="I6" s="57">
+      <c r="I6" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!L6)),COUNT(Сравнение!$L$5:$L$14)&lt;2),"",IF(MAX(Сравнение!$L$5:$L$14)=MIN(Сравнение!$L$5:$L$14),0.5,(Сравнение!L6-MIN(Сравнение!$L$5:$L$14))/(MAX(Сравнение!$L$5:$L$14)-MIN(Сравнение!$L$5:$L$14))))</f>
         <v/>
       </c>
       <c r="J6" s="36" t="n"/>
-      <c r="K6" s="58">
+      <c r="K6" s="57">
         <f>IF(OR(Сравнение!A6="",SUM(T6:AA6)=0),"",100*SUM(L6:S6)/SUM(T6:AA6))</f>
         <v/>
       </c>
@@ -2607,40 +2684,40 @@
         <f>IF(Сравнение!A7="","",Сравнение!A7)</f>
         <v/>
       </c>
-      <c r="B7" s="57">
+      <c r="B7" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!M7)),COUNT(Сравнение!$M$5:$M$14)&lt;2),"",IF(MAX(Сравнение!$M$5:$M$14)=MIN(Сравнение!$M$5:$M$14),0.5,(Сравнение!M7-MIN(Сравнение!$M$5:$M$14))/(MAX(Сравнение!$M$5:$M$14)-MIN(Сравнение!$M$5:$M$14))))</f>
         <v/>
       </c>
-      <c r="C7" s="57">
+      <c r="C7" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!N7)),COUNT(Сравнение!$N$5:$N$14)&lt;2),"",IF(MAX(Сравнение!$N$5:$N$14)=MIN(Сравнение!$N$5:$N$14),0.5,(Сравнение!N7-MIN(Сравнение!$N$5:$N$14))/(MAX(Сравнение!$N$5:$N$14)-MIN(Сравнение!$N$5:$N$14))))</f>
         <v/>
       </c>
-      <c r="D7" s="57">
+      <c r="D7" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!O7)),COUNT(Сравнение!$O$5:$O$14)&lt;2),"",IF(MAX(Сравнение!$O$5:$O$14)=MIN(Сравнение!$O$5:$O$14),0.5,(MAX(Сравнение!$O$5:$O$14)-Сравнение!O7)/(MAX(Сравнение!$O$5:$O$14)-MIN(Сравнение!$O$5:$O$14))))</f>
         <v/>
       </c>
-      <c r="E7" s="57">
+      <c r="E7" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!P7)),COUNT(Сравнение!$P$5:$P$14)&lt;2),"",IF(MAX(Сравнение!$P$5:$P$14)=MIN(Сравнение!$P$5:$P$14),0.5,(MAX(Сравнение!$P$5:$P$14)-Сравнение!P7)/(MAX(Сравнение!$P$5:$P$14)-MIN(Сравнение!$P$5:$P$14))))</f>
         <v/>
       </c>
-      <c r="F7" s="57">
+      <c r="F7" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!J7)),COUNT(Сравнение!$J$5:$J$14)&lt;2),"",IF(MAX(Сравнение!$J$5:$J$14)=MIN(Сравнение!$J$5:$J$14),0.5,(Сравнение!J7-MIN(Сравнение!$J$5:$J$14))/(MAX(Сравнение!$J$5:$J$14)-MIN(Сравнение!$J$5:$J$14))))</f>
         <v/>
       </c>
-      <c r="G7" s="57">
+      <c r="G7" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!K7)),COUNT(Сравнение!$K$5:$K$14)&lt;2),"",IF(MAX(Сравнение!$K$5:$K$14)=MIN(Сравнение!$K$5:$K$14),0.5,(MAX(Сравнение!$K$5:$K$14)-Сравнение!K7)/(MAX(Сравнение!$K$5:$K$14)-MIN(Сравнение!$K$5:$K$14))))</f>
         <v/>
       </c>
-      <c r="H7" s="57">
+      <c r="H7" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!Q7)),COUNT(Сравнение!$Q$5:$Q$14)&lt;2),"",IF(MAX(Сравнение!$Q$5:$Q$14)=MIN(Сравнение!$Q$5:$Q$14),0.5,(MAX(Сравнение!$Q$5:$Q$14)-Сравнение!Q7)/(MAX(Сравнение!$Q$5:$Q$14)-MIN(Сравнение!$Q$5:$Q$14))))</f>
         <v/>
       </c>
-      <c r="I7" s="57">
+      <c r="I7" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!L7)),COUNT(Сравнение!$L$5:$L$14)&lt;2),"",IF(MAX(Сравнение!$L$5:$L$14)=MIN(Сравнение!$L$5:$L$14),0.5,(Сравнение!L7-MIN(Сравнение!$L$5:$L$14))/(MAX(Сравнение!$L$5:$L$14)-MIN(Сравнение!$L$5:$L$14))))</f>
         <v/>
       </c>
       <c r="J7" s="36" t="n"/>
-      <c r="K7" s="58">
+      <c r="K7" s="57">
         <f>IF(OR(Сравнение!A7="",SUM(T7:AA7)=0),"",100*SUM(L7:S7)/SUM(T7:AA7))</f>
         <v/>
       </c>
@@ -2714,40 +2791,40 @@
         <f>IF(Сравнение!A8="","",Сравнение!A8)</f>
         <v/>
       </c>
-      <c r="B8" s="57">
+      <c r="B8" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!M8)),COUNT(Сравнение!$M$5:$M$14)&lt;2),"",IF(MAX(Сравнение!$M$5:$M$14)=MIN(Сравнение!$M$5:$M$14),0.5,(Сравнение!M8-MIN(Сравнение!$M$5:$M$14))/(MAX(Сравнение!$M$5:$M$14)-MIN(Сравнение!$M$5:$M$14))))</f>
         <v/>
       </c>
-      <c r="C8" s="57">
+      <c r="C8" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!N8)),COUNT(Сравнение!$N$5:$N$14)&lt;2),"",IF(MAX(Сравнение!$N$5:$N$14)=MIN(Сравнение!$N$5:$N$14),0.5,(Сравнение!N8-MIN(Сравнение!$N$5:$N$14))/(MAX(Сравнение!$N$5:$N$14)-MIN(Сравнение!$N$5:$N$14))))</f>
         <v/>
       </c>
-      <c r="D8" s="57">
+      <c r="D8" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!O8)),COUNT(Сравнение!$O$5:$O$14)&lt;2),"",IF(MAX(Сравнение!$O$5:$O$14)=MIN(Сравнение!$O$5:$O$14),0.5,(MAX(Сравнение!$O$5:$O$14)-Сравнение!O8)/(MAX(Сравнение!$O$5:$O$14)-MIN(Сравнение!$O$5:$O$14))))</f>
         <v/>
       </c>
-      <c r="E8" s="57">
+      <c r="E8" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!P8)),COUNT(Сравнение!$P$5:$P$14)&lt;2),"",IF(MAX(Сравнение!$P$5:$P$14)=MIN(Сравнение!$P$5:$P$14),0.5,(MAX(Сравнение!$P$5:$P$14)-Сравнение!P8)/(MAX(Сравнение!$P$5:$P$14)-MIN(Сравнение!$P$5:$P$14))))</f>
         <v/>
       </c>
-      <c r="F8" s="57">
+      <c r="F8" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!J8)),COUNT(Сравнение!$J$5:$J$14)&lt;2),"",IF(MAX(Сравнение!$J$5:$J$14)=MIN(Сравнение!$J$5:$J$14),0.5,(Сравнение!J8-MIN(Сравнение!$J$5:$J$14))/(MAX(Сравнение!$J$5:$J$14)-MIN(Сравнение!$J$5:$J$14))))</f>
         <v/>
       </c>
-      <c r="G8" s="57">
+      <c r="G8" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!K8)),COUNT(Сравнение!$K$5:$K$14)&lt;2),"",IF(MAX(Сравнение!$K$5:$K$14)=MIN(Сравнение!$K$5:$K$14),0.5,(MAX(Сравнение!$K$5:$K$14)-Сравнение!K8)/(MAX(Сравнение!$K$5:$K$14)-MIN(Сравнение!$K$5:$K$14))))</f>
         <v/>
       </c>
-      <c r="H8" s="57">
+      <c r="H8" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!Q8)),COUNT(Сравнение!$Q$5:$Q$14)&lt;2),"",IF(MAX(Сравнение!$Q$5:$Q$14)=MIN(Сравнение!$Q$5:$Q$14),0.5,(MAX(Сравнение!$Q$5:$Q$14)-Сравнение!Q8)/(MAX(Сравнение!$Q$5:$Q$14)-MIN(Сравнение!$Q$5:$Q$14))))</f>
         <v/>
       </c>
-      <c r="I8" s="57">
+      <c r="I8" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!L8)),COUNT(Сравнение!$L$5:$L$14)&lt;2),"",IF(MAX(Сравнение!$L$5:$L$14)=MIN(Сравнение!$L$5:$L$14),0.5,(Сравнение!L8-MIN(Сравнение!$L$5:$L$14))/(MAX(Сравнение!$L$5:$L$14)-MIN(Сравнение!$L$5:$L$14))))</f>
         <v/>
       </c>
       <c r="J8" s="36" t="n"/>
-      <c r="K8" s="58">
+      <c r="K8" s="57">
         <f>IF(OR(Сравнение!A8="",SUM(T8:AA8)=0),"",100*SUM(L8:S8)/SUM(T8:AA8))</f>
         <v/>
       </c>
@@ -2821,40 +2898,40 @@
         <f>IF(Сравнение!A9="","",Сравнение!A9)</f>
         <v/>
       </c>
-      <c r="B9" s="57">
+      <c r="B9" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!M9)),COUNT(Сравнение!$M$5:$M$14)&lt;2),"",IF(MAX(Сравнение!$M$5:$M$14)=MIN(Сравнение!$M$5:$M$14),0.5,(Сравнение!M9-MIN(Сравнение!$M$5:$M$14))/(MAX(Сравнение!$M$5:$M$14)-MIN(Сравнение!$M$5:$M$14))))</f>
         <v/>
       </c>
-      <c r="C9" s="57">
+      <c r="C9" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!N9)),COUNT(Сравнение!$N$5:$N$14)&lt;2),"",IF(MAX(Сравнение!$N$5:$N$14)=MIN(Сравнение!$N$5:$N$14),0.5,(Сравнение!N9-MIN(Сравнение!$N$5:$N$14))/(MAX(Сравнение!$N$5:$N$14)-MIN(Сравнение!$N$5:$N$14))))</f>
         <v/>
       </c>
-      <c r="D9" s="57">
+      <c r="D9" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!O9)),COUNT(Сравнение!$O$5:$O$14)&lt;2),"",IF(MAX(Сравнение!$O$5:$O$14)=MIN(Сравнение!$O$5:$O$14),0.5,(MAX(Сравнение!$O$5:$O$14)-Сравнение!O9)/(MAX(Сравнение!$O$5:$O$14)-MIN(Сравнение!$O$5:$O$14))))</f>
         <v/>
       </c>
-      <c r="E9" s="57">
+      <c r="E9" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!P9)),COUNT(Сравнение!$P$5:$P$14)&lt;2),"",IF(MAX(Сравнение!$P$5:$P$14)=MIN(Сравнение!$P$5:$P$14),0.5,(MAX(Сравнение!$P$5:$P$14)-Сравнение!P9)/(MAX(Сравнение!$P$5:$P$14)-MIN(Сравнение!$P$5:$P$14))))</f>
         <v/>
       </c>
-      <c r="F9" s="57">
+      <c r="F9" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!J9)),COUNT(Сравнение!$J$5:$J$14)&lt;2),"",IF(MAX(Сравнение!$J$5:$J$14)=MIN(Сравнение!$J$5:$J$14),0.5,(Сравнение!J9-MIN(Сравнение!$J$5:$J$14))/(MAX(Сравнение!$J$5:$J$14)-MIN(Сравнение!$J$5:$J$14))))</f>
         <v/>
       </c>
-      <c r="G9" s="57">
+      <c r="G9" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!K9)),COUNT(Сравнение!$K$5:$K$14)&lt;2),"",IF(MAX(Сравнение!$K$5:$K$14)=MIN(Сравнение!$K$5:$K$14),0.5,(MAX(Сравнение!$K$5:$K$14)-Сравнение!K9)/(MAX(Сравнение!$K$5:$K$14)-MIN(Сравнение!$K$5:$K$14))))</f>
         <v/>
       </c>
-      <c r="H9" s="57">
+      <c r="H9" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!Q9)),COUNT(Сравнение!$Q$5:$Q$14)&lt;2),"",IF(MAX(Сравнение!$Q$5:$Q$14)=MIN(Сравнение!$Q$5:$Q$14),0.5,(MAX(Сравнение!$Q$5:$Q$14)-Сравнение!Q9)/(MAX(Сравнение!$Q$5:$Q$14)-MIN(Сравнение!$Q$5:$Q$14))))</f>
         <v/>
       </c>
-      <c r="I9" s="57">
+      <c r="I9" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!L9)),COUNT(Сравнение!$L$5:$L$14)&lt;2),"",IF(MAX(Сравнение!$L$5:$L$14)=MIN(Сравнение!$L$5:$L$14),0.5,(Сравнение!L9-MIN(Сравнение!$L$5:$L$14))/(MAX(Сравнение!$L$5:$L$14)-MIN(Сравнение!$L$5:$L$14))))</f>
         <v/>
       </c>
       <c r="J9" s="36" t="n"/>
-      <c r="K9" s="58">
+      <c r="K9" s="57">
         <f>IF(OR(Сравнение!A9="",SUM(T9:AA9)=0),"",100*SUM(L9:S9)/SUM(T9:AA9))</f>
         <v/>
       </c>
@@ -2928,40 +3005,40 @@
         <f>IF(Сравнение!A10="","",Сравнение!A10)</f>
         <v/>
       </c>
-      <c r="B10" s="57">
+      <c r="B10" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!M10)),COUNT(Сравнение!$M$5:$M$14)&lt;2),"",IF(MAX(Сравнение!$M$5:$M$14)=MIN(Сравнение!$M$5:$M$14),0.5,(Сравнение!M10-MIN(Сравнение!$M$5:$M$14))/(MAX(Сравнение!$M$5:$M$14)-MIN(Сравнение!$M$5:$M$14))))</f>
         <v/>
       </c>
-      <c r="C10" s="57">
+      <c r="C10" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!N10)),COUNT(Сравнение!$N$5:$N$14)&lt;2),"",IF(MAX(Сравнение!$N$5:$N$14)=MIN(Сравнение!$N$5:$N$14),0.5,(Сравнение!N10-MIN(Сравнение!$N$5:$N$14))/(MAX(Сравнение!$N$5:$N$14)-MIN(Сравнение!$N$5:$N$14))))</f>
         <v/>
       </c>
-      <c r="D10" s="57">
+      <c r="D10" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!O10)),COUNT(Сравнение!$O$5:$O$14)&lt;2),"",IF(MAX(Сравнение!$O$5:$O$14)=MIN(Сравнение!$O$5:$O$14),0.5,(MAX(Сравнение!$O$5:$O$14)-Сравнение!O10)/(MAX(Сравнение!$O$5:$O$14)-MIN(Сравнение!$O$5:$O$14))))</f>
         <v/>
       </c>
-      <c r="E10" s="57">
+      <c r="E10" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!P10)),COUNT(Сравнение!$P$5:$P$14)&lt;2),"",IF(MAX(Сравнение!$P$5:$P$14)=MIN(Сравнение!$P$5:$P$14),0.5,(MAX(Сравнение!$P$5:$P$14)-Сравнение!P10)/(MAX(Сравнение!$P$5:$P$14)-MIN(Сравнение!$P$5:$P$14))))</f>
         <v/>
       </c>
-      <c r="F10" s="57">
+      <c r="F10" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!J10)),COUNT(Сравнение!$J$5:$J$14)&lt;2),"",IF(MAX(Сравнение!$J$5:$J$14)=MIN(Сравнение!$J$5:$J$14),0.5,(Сравнение!J10-MIN(Сравнение!$J$5:$J$14))/(MAX(Сравнение!$J$5:$J$14)-MIN(Сравнение!$J$5:$J$14))))</f>
         <v/>
       </c>
-      <c r="G10" s="57">
+      <c r="G10" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!K10)),COUNT(Сравнение!$K$5:$K$14)&lt;2),"",IF(MAX(Сравнение!$K$5:$K$14)=MIN(Сравнение!$K$5:$K$14),0.5,(MAX(Сравнение!$K$5:$K$14)-Сравнение!K10)/(MAX(Сравнение!$K$5:$K$14)-MIN(Сравнение!$K$5:$K$14))))</f>
         <v/>
       </c>
-      <c r="H10" s="57">
+      <c r="H10" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!Q10)),COUNT(Сравнение!$Q$5:$Q$14)&lt;2),"",IF(MAX(Сравнение!$Q$5:$Q$14)=MIN(Сравнение!$Q$5:$Q$14),0.5,(MAX(Сравнение!$Q$5:$Q$14)-Сравнение!Q10)/(MAX(Сравнение!$Q$5:$Q$14)-MIN(Сравнение!$Q$5:$Q$14))))</f>
         <v/>
       </c>
-      <c r="I10" s="57">
+      <c r="I10" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!L10)),COUNT(Сравнение!$L$5:$L$14)&lt;2),"",IF(MAX(Сравнение!$L$5:$L$14)=MIN(Сравнение!$L$5:$L$14),0.5,(Сравнение!L10-MIN(Сравнение!$L$5:$L$14))/(MAX(Сравнение!$L$5:$L$14)-MIN(Сравнение!$L$5:$L$14))))</f>
         <v/>
       </c>
       <c r="J10" s="36" t="n"/>
-      <c r="K10" s="58">
+      <c r="K10" s="57">
         <f>IF(OR(Сравнение!A10="",SUM(T10:AA10)=0),"",100*SUM(L10:S10)/SUM(T10:AA10))</f>
         <v/>
       </c>
@@ -3035,40 +3112,40 @@
         <f>IF(Сравнение!A11="","",Сравнение!A11)</f>
         <v/>
       </c>
-      <c r="B11" s="57">
+      <c r="B11" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!M11)),COUNT(Сравнение!$M$5:$M$14)&lt;2),"",IF(MAX(Сравнение!$M$5:$M$14)=MIN(Сравнение!$M$5:$M$14),0.5,(Сравнение!M11-MIN(Сравнение!$M$5:$M$14))/(MAX(Сравнение!$M$5:$M$14)-MIN(Сравнение!$M$5:$M$14))))</f>
         <v/>
       </c>
-      <c r="C11" s="57">
+      <c r="C11" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!N11)),COUNT(Сравнение!$N$5:$N$14)&lt;2),"",IF(MAX(Сравнение!$N$5:$N$14)=MIN(Сравнение!$N$5:$N$14),0.5,(Сравнение!N11-MIN(Сравнение!$N$5:$N$14))/(MAX(Сравнение!$N$5:$N$14)-MIN(Сравнение!$N$5:$N$14))))</f>
         <v/>
       </c>
-      <c r="D11" s="57">
+      <c r="D11" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!O11)),COUNT(Сравнение!$O$5:$O$14)&lt;2),"",IF(MAX(Сравнение!$O$5:$O$14)=MIN(Сравнение!$O$5:$O$14),0.5,(MAX(Сравнение!$O$5:$O$14)-Сравнение!O11)/(MAX(Сравнение!$O$5:$O$14)-MIN(Сравнение!$O$5:$O$14))))</f>
         <v/>
       </c>
-      <c r="E11" s="57">
+      <c r="E11" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!P11)),COUNT(Сравнение!$P$5:$P$14)&lt;2),"",IF(MAX(Сравнение!$P$5:$P$14)=MIN(Сравнение!$P$5:$P$14),0.5,(MAX(Сравнение!$P$5:$P$14)-Сравнение!P11)/(MAX(Сравнение!$P$5:$P$14)-MIN(Сравнение!$P$5:$P$14))))</f>
         <v/>
       </c>
-      <c r="F11" s="57">
+      <c r="F11" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!J11)),COUNT(Сравнение!$J$5:$J$14)&lt;2),"",IF(MAX(Сравнение!$J$5:$J$14)=MIN(Сравнение!$J$5:$J$14),0.5,(Сравнение!J11-MIN(Сравнение!$J$5:$J$14))/(MAX(Сравнение!$J$5:$J$14)-MIN(Сравнение!$J$5:$J$14))))</f>
         <v/>
       </c>
-      <c r="G11" s="57">
+      <c r="G11" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!K11)),COUNT(Сравнение!$K$5:$K$14)&lt;2),"",IF(MAX(Сравнение!$K$5:$K$14)=MIN(Сравнение!$K$5:$K$14),0.5,(MAX(Сравнение!$K$5:$K$14)-Сравнение!K11)/(MAX(Сравнение!$K$5:$K$14)-MIN(Сравнение!$K$5:$K$14))))</f>
         <v/>
       </c>
-      <c r="H11" s="57">
+      <c r="H11" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!Q11)),COUNT(Сравнение!$Q$5:$Q$14)&lt;2),"",IF(MAX(Сравнение!$Q$5:$Q$14)=MIN(Сравнение!$Q$5:$Q$14),0.5,(MAX(Сравнение!$Q$5:$Q$14)-Сравнение!Q11)/(MAX(Сравнение!$Q$5:$Q$14)-MIN(Сравнение!$Q$5:$Q$14))))</f>
         <v/>
       </c>
-      <c r="I11" s="57">
+      <c r="I11" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!L11)),COUNT(Сравнение!$L$5:$L$14)&lt;2),"",IF(MAX(Сравнение!$L$5:$L$14)=MIN(Сравнение!$L$5:$L$14),0.5,(Сравнение!L11-MIN(Сравнение!$L$5:$L$14))/(MAX(Сравнение!$L$5:$L$14)-MIN(Сравнение!$L$5:$L$14))))</f>
         <v/>
       </c>
       <c r="J11" s="36" t="n"/>
-      <c r="K11" s="58">
+      <c r="K11" s="57">
         <f>IF(OR(Сравнение!A11="",SUM(T11:AA11)=0),"",100*SUM(L11:S11)/SUM(T11:AA11))</f>
         <v/>
       </c>
@@ -3142,40 +3219,40 @@
         <f>IF(Сравнение!A12="","",Сравнение!A12)</f>
         <v/>
       </c>
-      <c r="B12" s="57">
+      <c r="B12" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!M12)),COUNT(Сравнение!$M$5:$M$14)&lt;2),"",IF(MAX(Сравнение!$M$5:$M$14)=MIN(Сравнение!$M$5:$M$14),0.5,(Сравнение!M12-MIN(Сравнение!$M$5:$M$14))/(MAX(Сравнение!$M$5:$M$14)-MIN(Сравнение!$M$5:$M$14))))</f>
         <v/>
       </c>
-      <c r="C12" s="57">
+      <c r="C12" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!N12)),COUNT(Сравнение!$N$5:$N$14)&lt;2),"",IF(MAX(Сравнение!$N$5:$N$14)=MIN(Сравнение!$N$5:$N$14),0.5,(Сравнение!N12-MIN(Сравнение!$N$5:$N$14))/(MAX(Сравнение!$N$5:$N$14)-MIN(Сравнение!$N$5:$N$14))))</f>
         <v/>
       </c>
-      <c r="D12" s="57">
+      <c r="D12" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!O12)),COUNT(Сравнение!$O$5:$O$14)&lt;2),"",IF(MAX(Сравнение!$O$5:$O$14)=MIN(Сравнение!$O$5:$O$14),0.5,(MAX(Сравнение!$O$5:$O$14)-Сравнение!O12)/(MAX(Сравнение!$O$5:$O$14)-MIN(Сравнение!$O$5:$O$14))))</f>
         <v/>
       </c>
-      <c r="E12" s="57">
+      <c r="E12" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!P12)),COUNT(Сравнение!$P$5:$P$14)&lt;2),"",IF(MAX(Сравнение!$P$5:$P$14)=MIN(Сравнение!$P$5:$P$14),0.5,(MAX(Сравнение!$P$5:$P$14)-Сравнение!P12)/(MAX(Сравнение!$P$5:$P$14)-MIN(Сравнение!$P$5:$P$14))))</f>
         <v/>
       </c>
-      <c r="F12" s="57">
+      <c r="F12" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!J12)),COUNT(Сравнение!$J$5:$J$14)&lt;2),"",IF(MAX(Сравнение!$J$5:$J$14)=MIN(Сравнение!$J$5:$J$14),0.5,(Сравнение!J12-MIN(Сравнение!$J$5:$J$14))/(MAX(Сравнение!$J$5:$J$14)-MIN(Сравнение!$J$5:$J$14))))</f>
         <v/>
       </c>
-      <c r="G12" s="57">
+      <c r="G12" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!K12)),COUNT(Сравнение!$K$5:$K$14)&lt;2),"",IF(MAX(Сравнение!$K$5:$K$14)=MIN(Сравнение!$K$5:$K$14),0.5,(MAX(Сравнение!$K$5:$K$14)-Сравнение!K12)/(MAX(Сравнение!$K$5:$K$14)-MIN(Сравнение!$K$5:$K$14))))</f>
         <v/>
       </c>
-      <c r="H12" s="57">
+      <c r="H12" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!Q12)),COUNT(Сравнение!$Q$5:$Q$14)&lt;2),"",IF(MAX(Сравнение!$Q$5:$Q$14)=MIN(Сравнение!$Q$5:$Q$14),0.5,(MAX(Сравнение!$Q$5:$Q$14)-Сравнение!Q12)/(MAX(Сравнение!$Q$5:$Q$14)-MIN(Сравнение!$Q$5:$Q$14))))</f>
         <v/>
       </c>
-      <c r="I12" s="57">
+      <c r="I12" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!L12)),COUNT(Сравнение!$L$5:$L$14)&lt;2),"",IF(MAX(Сравнение!$L$5:$L$14)=MIN(Сравнение!$L$5:$L$14),0.5,(Сравнение!L12-MIN(Сравнение!$L$5:$L$14))/(MAX(Сравнение!$L$5:$L$14)-MIN(Сравнение!$L$5:$L$14))))</f>
         <v/>
       </c>
       <c r="J12" s="36" t="n"/>
-      <c r="K12" s="58">
+      <c r="K12" s="57">
         <f>IF(OR(Сравнение!A12="",SUM(T12:AA12)=0),"",100*SUM(L12:S12)/SUM(T12:AA12))</f>
         <v/>
       </c>
@@ -3249,40 +3326,40 @@
         <f>IF(Сравнение!A13="","",Сравнение!A13)</f>
         <v/>
       </c>
-      <c r="B13" s="57">
+      <c r="B13" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!M13)),COUNT(Сравнение!$M$5:$M$14)&lt;2),"",IF(MAX(Сравнение!$M$5:$M$14)=MIN(Сравнение!$M$5:$M$14),0.5,(Сравнение!M13-MIN(Сравнение!$M$5:$M$14))/(MAX(Сравнение!$M$5:$M$14)-MIN(Сравнение!$M$5:$M$14))))</f>
         <v/>
       </c>
-      <c r="C13" s="57">
+      <c r="C13" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!N13)),COUNT(Сравнение!$N$5:$N$14)&lt;2),"",IF(MAX(Сравнение!$N$5:$N$14)=MIN(Сравнение!$N$5:$N$14),0.5,(Сравнение!N13-MIN(Сравнение!$N$5:$N$14))/(MAX(Сравнение!$N$5:$N$14)-MIN(Сравнение!$N$5:$N$14))))</f>
         <v/>
       </c>
-      <c r="D13" s="57">
+      <c r="D13" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!O13)),COUNT(Сравнение!$O$5:$O$14)&lt;2),"",IF(MAX(Сравнение!$O$5:$O$14)=MIN(Сравнение!$O$5:$O$14),0.5,(MAX(Сравнение!$O$5:$O$14)-Сравнение!O13)/(MAX(Сравнение!$O$5:$O$14)-MIN(Сравнение!$O$5:$O$14))))</f>
         <v/>
       </c>
-      <c r="E13" s="57">
+      <c r="E13" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!P13)),COUNT(Сравнение!$P$5:$P$14)&lt;2),"",IF(MAX(Сравнение!$P$5:$P$14)=MIN(Сравнение!$P$5:$P$14),0.5,(MAX(Сравнение!$P$5:$P$14)-Сравнение!P13)/(MAX(Сравнение!$P$5:$P$14)-MIN(Сравнение!$P$5:$P$14))))</f>
         <v/>
       </c>
-      <c r="F13" s="57">
+      <c r="F13" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!J13)),COUNT(Сравнение!$J$5:$J$14)&lt;2),"",IF(MAX(Сравнение!$J$5:$J$14)=MIN(Сравнение!$J$5:$J$14),0.5,(Сравнение!J13-MIN(Сравнение!$J$5:$J$14))/(MAX(Сравнение!$J$5:$J$14)-MIN(Сравнение!$J$5:$J$14))))</f>
         <v/>
       </c>
-      <c r="G13" s="57">
+      <c r="G13" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!K13)),COUNT(Сравнение!$K$5:$K$14)&lt;2),"",IF(MAX(Сравнение!$K$5:$K$14)=MIN(Сравнение!$K$5:$K$14),0.5,(MAX(Сравнение!$K$5:$K$14)-Сравнение!K13)/(MAX(Сравнение!$K$5:$K$14)-MIN(Сравнение!$K$5:$K$14))))</f>
         <v/>
       </c>
-      <c r="H13" s="57">
+      <c r="H13" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!Q13)),COUNT(Сравнение!$Q$5:$Q$14)&lt;2),"",IF(MAX(Сравнение!$Q$5:$Q$14)=MIN(Сравнение!$Q$5:$Q$14),0.5,(MAX(Сравнение!$Q$5:$Q$14)-Сравнение!Q13)/(MAX(Сравнение!$Q$5:$Q$14)-MIN(Сравнение!$Q$5:$Q$14))))</f>
         <v/>
       </c>
-      <c r="I13" s="57">
+      <c r="I13" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!L13)),COUNT(Сравнение!$L$5:$L$14)&lt;2),"",IF(MAX(Сравнение!$L$5:$L$14)=MIN(Сравнение!$L$5:$L$14),0.5,(Сравнение!L13-MIN(Сравнение!$L$5:$L$14))/(MAX(Сравнение!$L$5:$L$14)-MIN(Сравнение!$L$5:$L$14))))</f>
         <v/>
       </c>
       <c r="J13" s="36" t="n"/>
-      <c r="K13" s="58">
+      <c r="K13" s="57">
         <f>IF(OR(Сравнение!A13="",SUM(T13:AA13)=0),"",100*SUM(L13:S13)/SUM(T13:AA13))</f>
         <v/>
       </c>
@@ -3356,40 +3433,40 @@
         <f>IF(Сравнение!A14="","",Сравнение!A14)</f>
         <v/>
       </c>
-      <c r="B14" s="57">
+      <c r="B14" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!M14)),COUNT(Сравнение!$M$5:$M$14)&lt;2),"",IF(MAX(Сравнение!$M$5:$M$14)=MIN(Сравнение!$M$5:$M$14),0.5,(Сравнение!M14-MIN(Сравнение!$M$5:$M$14))/(MAX(Сравнение!$M$5:$M$14)-MIN(Сравнение!$M$5:$M$14))))</f>
         <v/>
       </c>
-      <c r="C14" s="57">
+      <c r="C14" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!N14)),COUNT(Сравнение!$N$5:$N$14)&lt;2),"",IF(MAX(Сравнение!$N$5:$N$14)=MIN(Сравнение!$N$5:$N$14),0.5,(Сравнение!N14-MIN(Сравнение!$N$5:$N$14))/(MAX(Сравнение!$N$5:$N$14)-MIN(Сравнение!$N$5:$N$14))))</f>
         <v/>
       </c>
-      <c r="D14" s="57">
+      <c r="D14" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!O14)),COUNT(Сравнение!$O$5:$O$14)&lt;2),"",IF(MAX(Сравнение!$O$5:$O$14)=MIN(Сравнение!$O$5:$O$14),0.5,(MAX(Сравнение!$O$5:$O$14)-Сравнение!O14)/(MAX(Сравнение!$O$5:$O$14)-MIN(Сравнение!$O$5:$O$14))))</f>
         <v/>
       </c>
-      <c r="E14" s="57">
+      <c r="E14" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!P14)),COUNT(Сравнение!$P$5:$P$14)&lt;2),"",IF(MAX(Сравнение!$P$5:$P$14)=MIN(Сравнение!$P$5:$P$14),0.5,(MAX(Сравнение!$P$5:$P$14)-Сравнение!P14)/(MAX(Сравнение!$P$5:$P$14)-MIN(Сравнение!$P$5:$P$14))))</f>
         <v/>
       </c>
-      <c r="F14" s="57">
+      <c r="F14" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!J14)),COUNT(Сравнение!$J$5:$J$14)&lt;2),"",IF(MAX(Сравнение!$J$5:$J$14)=MIN(Сравнение!$J$5:$J$14),0.5,(Сравнение!J14-MIN(Сравнение!$J$5:$J$14))/(MAX(Сравнение!$J$5:$J$14)-MIN(Сравнение!$J$5:$J$14))))</f>
         <v/>
       </c>
-      <c r="G14" s="57">
+      <c r="G14" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!K14)),COUNT(Сравнение!$K$5:$K$14)&lt;2),"",IF(MAX(Сравнение!$K$5:$K$14)=MIN(Сравнение!$K$5:$K$14),0.5,(MAX(Сравнение!$K$5:$K$14)-Сравнение!K14)/(MAX(Сравнение!$K$5:$K$14)-MIN(Сравнение!$K$5:$K$14))))</f>
         <v/>
       </c>
-      <c r="H14" s="57">
+      <c r="H14" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!Q14)),COUNT(Сравнение!$Q$5:$Q$14)&lt;2),"",IF(MAX(Сравнение!$Q$5:$Q$14)=MIN(Сравнение!$Q$5:$Q$14),0.5,(MAX(Сравнение!$Q$5:$Q$14)-Сравнение!Q14)/(MAX(Сравнение!$Q$5:$Q$14)-MIN(Сравнение!$Q$5:$Q$14))))</f>
         <v/>
       </c>
-      <c r="I14" s="57">
+      <c r="I14" s="56">
         <f>IF(OR(NOT(ISNUMBER(Сравнение!L14)),COUNT(Сравнение!$L$5:$L$14)&lt;2),"",IF(MAX(Сравнение!$L$5:$L$14)=MIN(Сравнение!$L$5:$L$14),0.5,(Сравнение!L14-MIN(Сравнение!$L$5:$L$14))/(MAX(Сравнение!$L$5:$L$14)-MIN(Сравнение!$L$5:$L$14))))</f>
         <v/>
       </c>
       <c r="J14" s="36" t="n"/>
-      <c r="K14" s="58">
+      <c r="K14" s="57">
         <f>IF(OR(Сравнение!A14="",SUM(T14:AA14)=0),"",100*SUM(L14:S14)/SUM(T14:AA14))</f>
         <v/>
       </c>
@@ -3480,7 +3557,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.35" customHeight="1" s="34">
-      <c r="A1" s="59" t="inlineStr">
+      <c r="A1" s="58" t="inlineStr">
         <is>
           <t>Веса метрик (меняй под себя)</t>
         </is>
@@ -3494,149 +3571,149 @@
       <c r="C2" s="36" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="34">
-      <c r="A3" s="60" t="inlineStr">
+      <c r="A3" s="59" t="inlineStr">
         <is>
           <t>Метрика</t>
         </is>
       </c>
-      <c r="B3" s="60" t="inlineStr">
+      <c r="B3" s="59" t="inlineStr">
         <is>
           <t>Вес</t>
         </is>
       </c>
-      <c r="C3" s="60" t="inlineStr">
+      <c r="C3" s="59" t="inlineStr">
         <is>
           <t>Направление</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="34">
-      <c r="A4" s="61" t="inlineStr">
+      <c r="A4" s="60" t="inlineStr">
         <is>
           <t>Рост TVL 6м</t>
         </is>
       </c>
-      <c r="B4" s="62" t="n">
+      <c r="B4" s="61" t="n">
         <v>15</v>
       </c>
-      <c r="C4" s="63" t="inlineStr">
+      <c r="C4" s="62" t="inlineStr">
         <is>
           <t>больше = лучше</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="34">
-      <c r="A5" s="61" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>Рост адресов 6м</t>
         </is>
       </c>
-      <c r="B5" s="62" t="n">
+      <c r="B5" s="61" t="n">
         <v>15</v>
       </c>
-      <c r="C5" s="63" t="inlineStr">
+      <c r="C5" s="62" t="inlineStr">
         <is>
           <t>больше = лучше</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="34">
-      <c r="A6" s="61" t="inlineStr">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>Mcap / TVL</t>
         </is>
       </c>
-      <c r="B6" s="62" t="n">
+      <c r="B6" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="C6" s="63" t="inlineStr">
+      <c r="C6" s="62" t="inlineStr">
         <is>
           <t>меньше = лучше</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="34">
-      <c r="A7" s="61" t="inlineStr">
+      <c r="A7" s="60" t="inlineStr">
         <is>
           <t>Mcap / Доход</t>
         </is>
       </c>
-      <c r="B7" s="62" t="n">
+      <c r="B7" s="61" t="n">
         <v>15</v>
       </c>
-      <c r="C7" s="63" t="inlineStr">
+      <c r="C7" s="62" t="inlineStr">
         <is>
           <t>меньше = лучше</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="34">
-      <c r="A8" s="61" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>Активных разработчиков</t>
         </is>
       </c>
-      <c r="B8" s="62" t="n">
+      <c r="B8" s="61" t="n">
         <v>15</v>
       </c>
-      <c r="C8" s="63" t="inlineStr">
+      <c r="C8" s="62" t="inlineStr">
         <is>
           <t>больше = лучше</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="34">
-      <c r="A9" s="61" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr">
         <is>
           <t>Разлок за 6 мес</t>
         </is>
       </c>
-      <c r="B9" s="62" t="n">
+      <c r="B9" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="C9" s="63" t="inlineStr">
+      <c r="C9" s="62" t="inlineStr">
         <is>
           <t>меньше = лучше</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="34">
-      <c r="A10" s="61" t="inlineStr">
+      <c r="A10" s="60" t="inlineStr">
         <is>
           <t>FDV / Mcap</t>
         </is>
       </c>
-      <c r="B10" s="62" t="n">
+      <c r="B10" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="C10" s="63" t="inlineStr">
+      <c r="C10" s="62" t="inlineStr">
         <is>
           <t>меньше = лучше</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="34">
-      <c r="A11" s="61" t="inlineStr">
+      <c r="A11" s="60" t="inlineStr">
         <is>
           <t>Инвесторы и команда</t>
         </is>
       </c>
-      <c r="B11" s="62" t="n">
+      <c r="B11" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="C11" s="63" t="inlineStr">
+      <c r="C11" s="62" t="inlineStr">
         <is>
           <t>больше = лучше</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="34">
-      <c r="A12" s="56" t="inlineStr">
+      <c r="A12" s="55" t="inlineStr">
         <is>
           <t>Сумма весов</t>
         </is>
       </c>
-      <c r="B12" s="56">
+      <c r="B12" s="55">
         <f>SUM(B4:B11)</f>
         <v/>
       </c>
@@ -3664,260 +3741,260 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.35" customHeight="1" s="34">
-      <c r="A1" s="59" t="inlineStr">
+      <c r="A1" s="58" t="inlineStr">
         <is>
           <t>Где брать цифры</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="34">
-      <c r="A3" s="64" t="inlineStr">
+      <c r="A3" s="63" t="inlineStr">
         <is>
           <t>Колонка</t>
         </is>
       </c>
-      <c r="B3" s="64" t="inlineStr">
+      <c r="B3" s="63" t="inlineStr">
         <is>
           <t>Источник</t>
         </is>
       </c>
-      <c r="C3" s="64" t="inlineStr">
+      <c r="C3" s="63" t="inlineStr">
         <is>
           <t>Ссылка</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="34">
-      <c r="A4" s="65" t="inlineStr">
+      <c r="A4" s="64" t="inlineStr">
         <is>
           <t>Капитализация, FDV</t>
         </is>
       </c>
-      <c r="B4" s="65" t="inlineStr">
+      <c r="B4" s="64" t="inlineStr">
         <is>
           <t>CoinGecko</t>
         </is>
       </c>
-      <c r="C4" s="66" t="inlineStr">
+      <c r="C4" s="65" t="inlineStr">
         <is>
           <t>https://www.coingecko.com/en/categories</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="34">
-      <c r="A5" s="65" t="inlineStr">
+      <c r="A5" s="64" t="inlineStr">
         <is>
           <t>TVL сейчас и 6 мес назад</t>
         </is>
       </c>
-      <c r="B5" s="65" t="inlineStr">
+      <c r="B5" s="64" t="inlineStr">
         <is>
           <t>DeFiLlama → Chains</t>
         </is>
       </c>
-      <c r="C5" s="66" t="inlineStr">
+      <c r="C5" s="65" t="inlineStr">
         <is>
           <t>https://defillama.com/chains</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="34">
-      <c r="A6" s="65" t="inlineStr">
+      <c r="A6" s="64" t="inlineStr">
         <is>
           <t>Активные адреса</t>
         </is>
       </c>
-      <c r="B6" s="65" t="inlineStr">
+      <c r="B6" s="64" t="inlineStr">
         <is>
           <t>Artemis</t>
         </is>
       </c>
-      <c r="C6" s="66" t="inlineStr">
+      <c r="C6" s="65" t="inlineStr">
         <is>
           <t>https://app.artemis.xyz</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="34">
-      <c r="A7" s="65" t="inlineStr">
+      <c r="A7" s="64" t="inlineStr">
         <is>
           <t>Доход / комиссии</t>
         </is>
       </c>
-      <c r="B7" s="65" t="inlineStr">
+      <c r="B7" s="64" t="inlineStr">
         <is>
           <t>DeFiLlama Fees</t>
         </is>
       </c>
-      <c r="C7" s="66" t="inlineStr">
+      <c r="C7" s="65" t="inlineStr">
         <is>
           <t>https://defillama.com/fees</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="34">
-      <c r="A8" s="65" t="inlineStr">
+      <c r="A8" s="64" t="inlineStr">
         <is>
           <t>Доход (альтернатива)</t>
         </is>
       </c>
-      <c r="B8" s="65" t="inlineStr">
+      <c r="B8" s="64" t="inlineStr">
         <is>
           <t>Token Terminal</t>
         </is>
       </c>
-      <c r="C8" s="66" t="inlineStr">
+      <c r="C8" s="65" t="inlineStr">
         <is>
           <t>https://tokenterminal.com</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="34">
-      <c r="A9" s="65" t="inlineStr">
+      <c r="A9" s="64" t="inlineStr">
         <is>
           <t>Разработчики</t>
         </is>
       </c>
-      <c r="B9" s="65" t="inlineStr">
+      <c r="B9" s="64" t="inlineStr">
         <is>
           <t>Artemis</t>
         </is>
       </c>
-      <c r="C9" s="66" t="inlineStr">
+      <c r="C9" s="65" t="inlineStr">
         <is>
           <t>https://app.artemis.xyz</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="34">
-      <c r="A10" s="65" t="inlineStr">
+      <c r="A10" s="64" t="inlineStr">
         <is>
           <t>Разлоки</t>
         </is>
       </c>
-      <c r="B10" s="65" t="inlineStr">
+      <c r="B10" s="64" t="inlineStr">
         <is>
           <t>Tokenomist</t>
         </is>
       </c>
-      <c r="C10" s="66" t="inlineStr">
+      <c r="C10" s="65" t="inlineStr">
         <is>
           <t>https://tokenomist.ai</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="34">
-      <c r="A11" s="65" t="inlineStr">
+      <c r="A11" s="64" t="inlineStr">
         <is>
           <t>Инвесторы, раунды</t>
         </is>
       </c>
-      <c r="B11" s="65" t="inlineStr">
+      <c r="B11" s="64" t="inlineStr">
         <is>
           <t>CryptoRank</t>
         </is>
       </c>
-      <c r="C11" s="66" t="inlineStr">
+      <c r="C11" s="65" t="inlineStr">
         <is>
           <t>https://cryptorank.io</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="34">
-      <c r="A12" s="65" t="inlineStr">
+      <c r="A12" s="64" t="inlineStr">
         <is>
           <t>Инвесторы, раунды</t>
         </is>
       </c>
-      <c r="B12" s="65" t="inlineStr">
+      <c r="B12" s="64" t="inlineStr">
         <is>
           <t>DeFiLlama Raises</t>
         </is>
       </c>
-      <c r="C12" s="66" t="inlineStr">
+      <c r="C12" s="65" t="inlineStr">
         <is>
           <t>https://defillama.com/raises</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="34">
-      <c r="A13" s="65" t="inlineStr">
+      <c r="A13" s="64" t="inlineStr">
         <is>
           <t>Метрики L2</t>
         </is>
       </c>
-      <c r="B13" s="65" t="inlineStr">
+      <c r="B13" s="64" t="inlineStr">
         <is>
           <t>growthepie</t>
         </is>
       </c>
-      <c r="C13" s="66" t="inlineStr">
+      <c r="C13" s="65" t="inlineStr">
         <is>
           <t>https://www.growthepie.xyz</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="34">
-      <c r="A14" s="65" t="inlineStr">
+      <c r="A14" s="64" t="inlineStr">
         <is>
           <t>Риски L2</t>
         </is>
       </c>
-      <c r="B14" s="65" t="inlineStr">
+      <c r="B14" s="64" t="inlineStr">
         <is>
           <t>L2BEAT</t>
         </is>
       </c>
-      <c r="C14" s="66" t="inlineStr">
+      <c r="C14" s="65" t="inlineStr">
         <is>
           <t>https://l2beat.com</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="34">
-      <c r="A17" s="67" t="inlineStr">
+      <c r="A17" s="66" t="inlineStr">
         <is>
           <t>Как пользоваться:</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="34">
-      <c r="A18" s="68" t="inlineStr">
+      <c r="A18" s="67" t="inlineStr">
         <is>
           <t>1. На листе «Сравнение» замени строки «Пример» своими сетями (до 10 штук).</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="34">
-      <c r="A19" s="68" t="inlineStr">
+      <c r="A19" s="67" t="inlineStr">
         <is>
           <t>2. Заполняй жёлтые ячейки. Пустые метрики просто не учитываются в балле.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="34">
-      <c r="A20" s="68" t="inlineStr">
+      <c r="A20" s="67" t="inlineStr">
         <is>
           <t>3. Для балла нужно минимум 2 сети с данными по метрике.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="34">
-      <c r="A21" s="68" t="inlineStr">
+      <c r="A21" s="67" t="inlineStr">
         <is>
           <t>4. Веса метрик меняй на листе «Веса».</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="34">
-      <c r="A22" s="68" t="inlineStr">
+      <c r="A22" s="67" t="inlineStr">
         <is>
           <t>5. Разлок вводи в процентах (3% = 3%), инвесторов — оценкой 1–5 по своему мнению.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="34">
-      <c r="A23" s="68" t="inlineStr">
+      <c r="A23" s="67" t="inlineStr">
         <is>
           <t>Балл относительный и не является рекомендацией к покупке.</t>
         </is>
@@ -3960,34 +4037,34 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="69" t="inlineStr">
+      <c r="A1" s="68" t="inlineStr">
         <is>
           <t>Откуда взята каждая цифра (сбор 30.09.2026)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="70" t="inlineStr">
+      <c r="A3" s="69" t="inlineStr">
         <is>
           <t>Экосистема</t>
         </is>
       </c>
-      <c r="B3" s="70" t="inlineStr">
+      <c r="B3" s="69" t="inlineStr">
         <is>
           <t>Метрика</t>
         </is>
       </c>
-      <c r="C3" s="70" t="inlineStr">
+      <c r="C3" s="69" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="D3" s="70" t="inlineStr">
+      <c r="D3" s="69" t="inlineStr">
         <is>
           <t>Источник</t>
         </is>
       </c>
-      <c r="E3" s="70" t="inlineStr">
+      <c r="E3" s="69" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
@@ -4004,8 +4081,8 @@
           <t>Капитализация, $ млн</t>
         </is>
       </c>
-      <c r="C4" s="71" t="n">
-        <v>327258.690254</v>
+      <c r="C4" s="70" t="n">
+        <v>327944.680337</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4025,8 +4102,8 @@
           <t>FDV, $ млн</t>
         </is>
       </c>
-      <c r="C5" s="71" t="n">
-        <v>327258.690254</v>
+      <c r="C5" s="70" t="n">
+        <v>327944.680337</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4046,8 +4123,8 @@
           <t>TVL сейчас, $ млн</t>
         </is>
       </c>
-      <c r="C6" s="71" t="n">
-        <v>53918.369868</v>
+      <c r="C6" s="70" t="n">
+        <v>53303.04256</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4071,7 +4148,7 @@
           <t>TVL 6 мес назад, $ млн</t>
         </is>
       </c>
-      <c r="C7" s="71" t="n">
+      <c r="C7" s="70" t="n">
         <v>53909.531522</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -4096,7 +4173,7 @@
           <t>Активные адреса/день сейчас</t>
         </is>
       </c>
-      <c r="C8" s="71" t="n">
+      <c r="C8" s="70" t="n">
         <v>495105</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -4121,7 +4198,7 @@
           <t>Активные адреса/день 6 мес назад</t>
         </is>
       </c>
-      <c r="C9" s="71" t="n">
+      <c r="C9" s="70" t="n">
         <v>616284</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -4146,7 +4223,7 @@
           <t>Доход/комиссии за год, $ млн</t>
         </is>
       </c>
-      <c r="C10" s="71" t="n">
+      <c r="C10" s="70" t="n">
         <v>202.689948</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -4161,61 +4238,67 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="72" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Ethereum</t>
         </is>
       </c>
-      <c r="B11" s="72" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Активных разработчиков/мес</t>
         </is>
       </c>
-      <c r="C11" s="73" t="n"/>
-      <c r="D11" s="72" t="inlineStr">
+      <c r="C11" s="70" t="n">
+        <v>3270</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Open Dev Data</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="71" t="inlineStr">
+        <is>
+          <t>Ethereum</t>
+        </is>
+      </c>
+      <c r="B12" s="71" t="inlineStr">
+        <is>
+          <t>Разлок за 6 мес, % предложения</t>
+        </is>
+      </c>
+      <c r="C12" s="72" t="n"/>
+      <c r="D12" s="71" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
         </is>
       </c>
-      <c r="E11" s="72" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="72" t="inlineStr">
+      <c r="E12" s="71" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="71" t="inlineStr">
         <is>
           <t>Ethereum</t>
         </is>
       </c>
-      <c r="B12" s="72" t="inlineStr">
-        <is>
-          <t>Разлок за 6 мес, % предложения</t>
-        </is>
-      </c>
-      <c r="C12" s="74" t="n"/>
-      <c r="D12" s="72" t="inlineStr">
+      <c r="B13" s="71" t="inlineStr">
+        <is>
+          <t>Инвесторы и команда, 1–5</t>
+        </is>
+      </c>
+      <c r="C13" s="73" t="n"/>
+      <c r="D13" s="71" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
         </is>
       </c>
-      <c r="E12" s="72" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="72" t="inlineStr">
-        <is>
-          <t>Ethereum</t>
-        </is>
-      </c>
-      <c r="B13" s="72" t="inlineStr">
-        <is>
-          <t>Инвесторы и команда, 1–5</t>
-        </is>
-      </c>
-      <c r="C13" s="73" t="n"/>
-      <c r="D13" s="72" t="inlineStr">
-        <is>
-          <t>нет данных — заполнить вручную</t>
-        </is>
-      </c>
-      <c r="E13" s="72" t="inlineStr"/>
+      <c r="E13" s="71" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4228,8 +4311,8 @@
           <t>Капитализация, $ млн</t>
         </is>
       </c>
-      <c r="C14" s="71" t="n">
-        <v>69988.26169699999</v>
+      <c r="C14" s="70" t="n">
+        <v>70355.204557</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -4249,8 +4332,8 @@
           <t>FDV, $ млн</t>
         </is>
       </c>
-      <c r="C15" s="71" t="n">
-        <v>75581.369252</v>
+      <c r="C15" s="70" t="n">
+        <v>75977.633946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4270,8 +4353,8 @@
           <t>TVL сейчас, $ млн</t>
         </is>
       </c>
-      <c r="C16" s="71" t="n">
-        <v>6471.36886</v>
+      <c r="C16" s="70" t="n">
+        <v>6568.178533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4295,7 +4378,7 @@
           <t>TVL 6 мес назад, $ млн</t>
         </is>
       </c>
-      <c r="C17" s="71" t="n">
+      <c r="C17" s="70" t="n">
         <v>6357.767767</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -4320,7 +4403,7 @@
           <t>Активные адреса/день сейчас</t>
         </is>
       </c>
-      <c r="C18" s="71" t="n">
+      <c r="C18" s="70" t="n">
         <v>5123259</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -4345,7 +4428,7 @@
           <t>Активные адреса/день 6 мес назад</t>
         </is>
       </c>
-      <c r="C19" s="71" t="n">
+      <c r="C19" s="70" t="n">
         <v>4289374</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -4370,7 +4453,7 @@
           <t>Доход/комиссии за год, $ млн</t>
         </is>
       </c>
-      <c r="C20" s="71" t="n">
+      <c r="C20" s="70" t="n">
         <v>239.426752</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -4385,61 +4468,67 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="72" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Solana</t>
         </is>
       </c>
-      <c r="B21" s="72" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Активных разработчиков/мес</t>
         </is>
       </c>
-      <c r="C21" s="73" t="n"/>
-      <c r="D21" s="72" t="inlineStr">
+      <c r="C21" s="70" t="n">
+        <v>1080</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Open Dev Data</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="71" t="inlineStr">
+        <is>
+          <t>Solana</t>
+        </is>
+      </c>
+      <c r="B22" s="71" t="inlineStr">
+        <is>
+          <t>Разлок за 6 мес, % предложения</t>
+        </is>
+      </c>
+      <c r="C22" s="72" t="n"/>
+      <c r="D22" s="71" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
         </is>
       </c>
-      <c r="E21" s="72" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="72" t="inlineStr">
+      <c r="E22" s="71" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="71" t="inlineStr">
         <is>
           <t>Solana</t>
         </is>
       </c>
-      <c r="B22" s="72" t="inlineStr">
-        <is>
-          <t>Разлок за 6 мес, % предложения</t>
-        </is>
-      </c>
-      <c r="C22" s="74" t="n"/>
-      <c r="D22" s="72" t="inlineStr">
+      <c r="B23" s="71" t="inlineStr">
+        <is>
+          <t>Инвесторы и команда, 1–5</t>
+        </is>
+      </c>
+      <c r="C23" s="73" t="n"/>
+      <c r="D23" s="71" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
         </is>
       </c>
-      <c r="E22" s="72" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="72" t="inlineStr">
-        <is>
-          <t>Solana</t>
-        </is>
-      </c>
-      <c r="B23" s="72" t="inlineStr">
-        <is>
-          <t>Инвесторы и команда, 1–5</t>
-        </is>
-      </c>
-      <c r="C23" s="73" t="n"/>
-      <c r="D23" s="72" t="inlineStr">
-        <is>
-          <t>нет данных — заполнить вручную</t>
-        </is>
-      </c>
-      <c r="E23" s="72" t="inlineStr"/>
+      <c r="E23" s="71" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4452,8 +4541,8 @@
           <t>Капитализация, $ млн</t>
         </is>
       </c>
-      <c r="C24" s="71" t="n">
-        <v>4767.521283</v>
+      <c r="C24" s="70" t="n">
+        <v>4865.721245</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4473,8 +4562,8 @@
           <t>FDV, $ млн</t>
         </is>
       </c>
-      <c r="C25" s="71" t="n">
-        <v>11637.930067</v>
+      <c r="C25" s="70" t="n">
+        <v>11877.644633</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4494,8 +4583,8 @@
           <t>TVL сейчас, $ млн</t>
         </is>
       </c>
-      <c r="C26" s="71" t="n">
-        <v>559.329125</v>
+      <c r="C26" s="70" t="n">
+        <v>551.750347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4519,7 +4608,7 @@
           <t>TVL 6 мес назад, $ млн</t>
         </is>
       </c>
-      <c r="C27" s="71" t="n">
+      <c r="C27" s="70" t="n">
         <v>570.720387</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -4544,7 +4633,7 @@
           <t>Активные адреса/день сейчас</t>
         </is>
       </c>
-      <c r="C28" s="71" t="n">
+      <c r="C28" s="70" t="n">
         <v>134536</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -4569,7 +4658,7 @@
           <t>Активные адреса/день 6 мес назад</t>
         </is>
       </c>
-      <c r="C29" s="71" t="n">
+      <c r="C29" s="70" t="n">
         <v>229146</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -4594,7 +4683,7 @@
           <t>Доход/комиссии за год, $ млн</t>
         </is>
       </c>
-      <c r="C30" s="71" t="n">
+      <c r="C30" s="70" t="n">
         <v>3.512066</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -4609,61 +4698,67 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="72" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Sui</t>
         </is>
       </c>
-      <c r="B31" s="72" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Активных разработчиков/мес</t>
         </is>
       </c>
-      <c r="C31" s="73" t="n"/>
-      <c r="D31" s="72" t="inlineStr">
+      <c r="C31" s="70" t="n">
+        <v>254</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Open Dev Data</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="71" t="inlineStr">
+        <is>
+          <t>Sui</t>
+        </is>
+      </c>
+      <c r="B32" s="71" t="inlineStr">
+        <is>
+          <t>Разлок за 6 мес, % предложения</t>
+        </is>
+      </c>
+      <c r="C32" s="72" t="n"/>
+      <c r="D32" s="71" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
         </is>
       </c>
-      <c r="E31" s="72" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="72" t="inlineStr">
+      <c r="E32" s="71" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="71" t="inlineStr">
         <is>
           <t>Sui</t>
         </is>
       </c>
-      <c r="B32" s="72" t="inlineStr">
-        <is>
-          <t>Разлок за 6 мес, % предложения</t>
-        </is>
-      </c>
-      <c r="C32" s="74" t="n"/>
-      <c r="D32" s="72" t="inlineStr">
+      <c r="B33" s="71" t="inlineStr">
+        <is>
+          <t>Инвесторы и команда, 1–5</t>
+        </is>
+      </c>
+      <c r="C33" s="73" t="n"/>
+      <c r="D33" s="71" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
         </is>
       </c>
-      <c r="E32" s="72" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="72" t="inlineStr">
-        <is>
-          <t>Sui</t>
-        </is>
-      </c>
-      <c r="B33" s="72" t="inlineStr">
-        <is>
-          <t>Инвесторы и команда, 1–5</t>
-        </is>
-      </c>
-      <c r="C33" s="73" t="n"/>
-      <c r="D33" s="72" t="inlineStr">
-        <is>
-          <t>нет данных — заполнить вручную</t>
-        </is>
-      </c>
-      <c r="E33" s="72" t="inlineStr"/>
+      <c r="E33" s="71" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4676,8 +4771,8 @@
           <t>Капитализация, $ млн</t>
         </is>
       </c>
-      <c r="C34" s="71" t="n">
-        <v>687.9191049999999</v>
+      <c r="C34" s="70" t="n">
+        <v>690.49137</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4697,8 +4792,8 @@
           <t>FDV, $ млн</t>
         </is>
       </c>
-      <c r="C35" s="71" t="n">
-        <v>955.210046</v>
+      <c r="C35" s="70" t="n">
+        <v>958.7853270000001</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4718,8 +4813,8 @@
           <t>TVL сейчас, $ млн</t>
         </is>
       </c>
-      <c r="C36" s="71" t="n">
-        <v>55.740282</v>
+      <c r="C36" s="70" t="n">
+        <v>55.53995</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4743,7 +4838,7 @@
           <t>TVL 6 мес назад, $ млн</t>
         </is>
       </c>
-      <c r="C37" s="71" t="n">
+      <c r="C37" s="70" t="n">
         <v>285.748159</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -4758,25 +4853,25 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="75" t="inlineStr">
+      <c r="A38" s="74" t="inlineStr">
         <is>
           <t>Aptos</t>
         </is>
       </c>
-      <c r="B38" s="75" t="inlineStr">
+      <c r="B38" s="74" t="inlineStr">
         <is>
           <t>Активные адреса/день сейчас</t>
         </is>
       </c>
-      <c r="C38" s="76" t="n">
+      <c r="C38" s="75" t="n">
         <v>35921</v>
       </c>
-      <c r="D38" s="75" t="inlineStr">
+      <c r="D38" s="74" t="inlineStr">
         <is>
           <t>Artemis</t>
         </is>
       </c>
-      <c r="E38" s="75" t="inlineStr">
+      <c r="E38" s="74" t="inlineStr">
         <is>
           <t>медиана за 7 дн до 2026-09-29. ⚠ изменение за 6 мес больше чем в 10 раз — проверь, реально ли это</t>
         </is>
@@ -4793,7 +4888,7 @@
           <t>Активные адреса/день 6 мес назад</t>
         </is>
       </c>
-      <c r="C39" s="71" t="n">
+      <c r="C39" s="70" t="n">
         <v>1055333</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -4818,7 +4913,7 @@
           <t>Доход/комиссии за год, $ млн</t>
         </is>
       </c>
-      <c r="C40" s="71" t="n">
+      <c r="C40" s="70" t="n">
         <v>1.145126</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -4833,61 +4928,67 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="72" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Aptos</t>
         </is>
       </c>
-      <c r="B41" s="72" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Активных разработчиков/мес</t>
         </is>
       </c>
-      <c r="C41" s="73" t="n"/>
-      <c r="D41" s="72" t="inlineStr">
+      <c r="C41" s="70" t="n">
+        <v>92</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Open Dev Data</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="71" t="inlineStr">
+        <is>
+          <t>Aptos</t>
+        </is>
+      </c>
+      <c r="B42" s="71" t="inlineStr">
+        <is>
+          <t>Разлок за 6 мес, % предложения</t>
+        </is>
+      </c>
+      <c r="C42" s="72" t="n"/>
+      <c r="D42" s="71" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
         </is>
       </c>
-      <c r="E41" s="72" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="72" t="inlineStr">
+      <c r="E42" s="71" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="71" t="inlineStr">
         <is>
           <t>Aptos</t>
         </is>
       </c>
-      <c r="B42" s="72" t="inlineStr">
-        <is>
-          <t>Разлок за 6 мес, % предложения</t>
-        </is>
-      </c>
-      <c r="C42" s="74" t="n"/>
-      <c r="D42" s="72" t="inlineStr">
+      <c r="B43" s="71" t="inlineStr">
+        <is>
+          <t>Инвесторы и команда, 1–5</t>
+        </is>
+      </c>
+      <c r="C43" s="73" t="n"/>
+      <c r="D43" s="71" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
         </is>
       </c>
-      <c r="E42" s="72" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="72" t="inlineStr">
-        <is>
-          <t>Aptos</t>
-        </is>
-      </c>
-      <c r="B43" s="72" t="inlineStr">
-        <is>
-          <t>Инвесторы и команда, 1–5</t>
-        </is>
-      </c>
-      <c r="C43" s="73" t="n"/>
-      <c r="D43" s="72" t="inlineStr">
-        <is>
-          <t>нет данных — заполнить вручную</t>
-        </is>
-      </c>
-      <c r="E43" s="72" t="inlineStr"/>
+      <c r="E43" s="71" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4900,8 +5001,8 @@
           <t>Капитализация, $ млн</t>
         </is>
       </c>
-      <c r="C44" s="71" t="n">
-        <v>4829.34046</v>
+      <c r="C44" s="70" t="n">
+        <v>4879.641119</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4921,8 +5022,8 @@
           <t>FDV, $ млн</t>
         </is>
       </c>
-      <c r="C45" s="71" t="n">
-        <v>5120.001442</v>
+      <c r="C45" s="70" t="n">
+        <v>5173.313795</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4942,8 +5043,8 @@
           <t>TVL сейчас, $ млн</t>
         </is>
       </c>
-      <c r="C46" s="71" t="n">
-        <v>640.767554</v>
+      <c r="C46" s="70" t="n">
+        <v>626.279733</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4967,7 +5068,7 @@
           <t>TVL 6 мес назад, $ млн</t>
         </is>
       </c>
-      <c r="C47" s="71" t="n">
+      <c r="C47" s="70" t="n">
         <v>724.301796</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -4982,50 +5083,50 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="75" t="inlineStr">
+      <c r="A48" s="74" t="inlineStr">
         <is>
           <t>Avalanche</t>
         </is>
       </c>
-      <c r="B48" s="75" t="inlineStr">
+      <c r="B48" s="74" t="inlineStr">
         <is>
           <t>Активные адреса/день сейчас</t>
         </is>
       </c>
-      <c r="C48" s="76" t="n">
+      <c r="C48" s="75" t="n">
         <v>21091</v>
       </c>
-      <c r="D48" s="75" t="inlineStr">
+      <c r="D48" s="74" t="inlineStr">
         <is>
           <t>Artemis</t>
         </is>
       </c>
-      <c r="E48" s="75" t="inlineStr">
+      <c r="E48" s="74" t="inlineStr">
         <is>
           <t>медиана за 7 дн до 2026-09-29. ⚠ ступенька в данных около 2026-07-11: медиана 502,037 → 22,052 за неделю — возможна смена методики источника, проверь вручную</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="75" t="inlineStr">
+      <c r="A49" s="74" t="inlineStr">
         <is>
           <t>Avalanche</t>
         </is>
       </c>
-      <c r="B49" s="75" t="inlineStr">
+      <c r="B49" s="74" t="inlineStr">
         <is>
           <t>Активные адреса/день 6 мес назад</t>
         </is>
       </c>
-      <c r="C49" s="76" t="n">
+      <c r="C49" s="75" t="n">
         <v>643627</v>
       </c>
-      <c r="D49" s="75" t="inlineStr">
+      <c r="D49" s="74" t="inlineStr">
         <is>
           <t>Artemis</t>
         </is>
       </c>
-      <c r="E49" s="75" t="inlineStr">
+      <c r="E49" s="74" t="inlineStr">
         <is>
           <t>медиана за 7 дн до 2026-04-01. ⚠ ступенька в данных около 2026-07-11: медиана 502,037 → 22,052 за неделю — возможна смена методики источника, проверь вручную</t>
         </is>
@@ -5042,7 +5143,7 @@
           <t>Доход/комиссии за год, $ млн</t>
         </is>
       </c>
-      <c r="C50" s="71" t="n">
+      <c r="C50" s="70" t="n">
         <v>4.076565</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -5057,61 +5158,67 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="72" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Avalanche</t>
         </is>
       </c>
-      <c r="B51" s="72" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Активных разработчиков/мес</t>
         </is>
       </c>
-      <c r="C51" s="73" t="n"/>
-      <c r="D51" s="72" t="inlineStr">
+      <c r="C51" s="70" t="n">
+        <v>108</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Open Dev Data</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="71" t="inlineStr">
+        <is>
+          <t>Avalanche</t>
+        </is>
+      </c>
+      <c r="B52" s="71" t="inlineStr">
+        <is>
+          <t>Разлок за 6 мес, % предложения</t>
+        </is>
+      </c>
+      <c r="C52" s="72" t="n"/>
+      <c r="D52" s="71" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
         </is>
       </c>
-      <c r="E51" s="72" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="72" t="inlineStr">
+      <c r="E52" s="71" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="71" t="inlineStr">
         <is>
           <t>Avalanche</t>
         </is>
       </c>
-      <c r="B52" s="72" t="inlineStr">
-        <is>
-          <t>Разлок за 6 мес, % предложения</t>
-        </is>
-      </c>
-      <c r="C52" s="74" t="n"/>
-      <c r="D52" s="72" t="inlineStr">
+      <c r="B53" s="71" t="inlineStr">
+        <is>
+          <t>Инвесторы и команда, 1–5</t>
+        </is>
+      </c>
+      <c r="C53" s="73" t="n"/>
+      <c r="D53" s="71" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
         </is>
       </c>
-      <c r="E52" s="72" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="72" t="inlineStr">
-        <is>
-          <t>Avalanche</t>
-        </is>
-      </c>
-      <c r="B53" s="72" t="inlineStr">
-        <is>
-          <t>Инвесторы и команда, 1–5</t>
-        </is>
-      </c>
-      <c r="C53" s="73" t="n"/>
-      <c r="D53" s="72" t="inlineStr">
-        <is>
-          <t>нет данных — заполнить вручную</t>
-        </is>
-      </c>
-      <c r="E53" s="72" t="inlineStr"/>
+      <c r="E53" s="71" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5124,8 +5231,8 @@
           <t>Капитализация, $ млн</t>
         </is>
       </c>
-      <c r="C54" s="71" t="n">
-        <v>6908.777867</v>
+      <c r="C54" s="70" t="n">
+        <v>7048.836656</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5145,8 +5252,8 @@
           <t>FDV, $ млн</t>
         </is>
       </c>
-      <c r="C55" s="71" t="n">
-        <v>6908.778987</v>
+      <c r="C55" s="70" t="n">
+        <v>7048.837611</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5166,8 +5273,8 @@
           <t>TVL сейчас, $ млн</t>
         </is>
       </c>
-      <c r="C56" s="71" t="n">
-        <v>239.929727</v>
+      <c r="C56" s="70" t="n">
+        <v>236.616937</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5191,7 +5298,7 @@
           <t>TVL 6 мес назад, $ млн</t>
         </is>
       </c>
-      <c r="C57" s="71" t="n">
+      <c r="C57" s="70" t="n">
         <v>95.21909100000001</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -5206,50 +5313,50 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="75" t="inlineStr">
+      <c r="A58" s="74" t="inlineStr">
         <is>
           <t>Near</t>
         </is>
       </c>
-      <c r="B58" s="75" t="inlineStr">
+      <c r="B58" s="74" t="inlineStr">
         <is>
           <t>Активные адреса/день сейчас</t>
         </is>
       </c>
-      <c r="C58" s="76" t="n">
+      <c r="C58" s="75" t="n">
         <v>76790</v>
       </c>
-      <c r="D58" s="75" t="inlineStr">
+      <c r="D58" s="74" t="inlineStr">
         <is>
           <t>Artemis</t>
         </is>
       </c>
-      <c r="E58" s="75" t="inlineStr">
+      <c r="E58" s="74" t="inlineStr">
         <is>
           <t>медиана за 7 дн до 2026-09-29. ⚠ ступенька в данных около 2026-03-30: медиана 3,067,142 → 472,650 за неделю — возможна смена методики источника, проверь вручную</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="75" t="inlineStr">
+      <c r="A59" s="74" t="inlineStr">
         <is>
           <t>Near</t>
         </is>
       </c>
-      <c r="B59" s="75" t="inlineStr">
+      <c r="B59" s="74" t="inlineStr">
         <is>
           <t>Активные адреса/день 6 мес назад</t>
         </is>
       </c>
-      <c r="C59" s="76" t="n">
+      <c r="C59" s="75" t="n">
         <v>3067142</v>
       </c>
-      <c r="D59" s="75" t="inlineStr">
+      <c r="D59" s="74" t="inlineStr">
         <is>
           <t>Artemis</t>
         </is>
       </c>
-      <c r="E59" s="75" t="inlineStr">
+      <c r="E59" s="74" t="inlineStr">
         <is>
           <t>медиана за 7 дн до 2026-04-01. ⚠ ступенька в данных около 2026-03-30: медиана 3,067,142 → 472,650 за неделю — возможна смена методики источника, проверь вручную</t>
         </is>
@@ -5266,7 +5373,7 @@
           <t>Доход/комиссии за год, $ млн</t>
         </is>
       </c>
-      <c r="C60" s="71" t="n">
+      <c r="C60" s="70" t="n">
         <v>1.261909</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -5281,61 +5388,67 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="72" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Near</t>
         </is>
       </c>
-      <c r="B61" s="72" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Активных разработчиков/мес</t>
         </is>
       </c>
-      <c r="C61" s="73" t="n"/>
-      <c r="D61" s="72" t="inlineStr">
+      <c r="C61" s="70" t="n">
+        <v>150</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Open Dev Data</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="71" t="inlineStr">
+        <is>
+          <t>Near</t>
+        </is>
+      </c>
+      <c r="B62" s="71" t="inlineStr">
+        <is>
+          <t>Разлок за 6 мес, % предложения</t>
+        </is>
+      </c>
+      <c r="C62" s="72" t="n"/>
+      <c r="D62" s="71" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
         </is>
       </c>
-      <c r="E61" s="72" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="72" t="inlineStr">
+      <c r="E62" s="71" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="71" t="inlineStr">
         <is>
           <t>Near</t>
         </is>
       </c>
-      <c r="B62" s="72" t="inlineStr">
-        <is>
-          <t>Разлок за 6 мес, % предложения</t>
-        </is>
-      </c>
-      <c r="C62" s="74" t="n"/>
-      <c r="D62" s="72" t="inlineStr">
+      <c r="B63" s="71" t="inlineStr">
+        <is>
+          <t>Инвесторы и команда, 1–5</t>
+        </is>
+      </c>
+      <c r="C63" s="73" t="n"/>
+      <c r="D63" s="71" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
         </is>
       </c>
-      <c r="E62" s="72" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="72" t="inlineStr">
-        <is>
-          <t>Near</t>
-        </is>
-      </c>
-      <c r="B63" s="72" t="inlineStr">
-        <is>
-          <t>Инвесторы и команда, 1–5</t>
-        </is>
-      </c>
-      <c r="C63" s="73" t="n"/>
-      <c r="D63" s="72" t="inlineStr">
-        <is>
-          <t>нет данных — заполнить вручную</t>
-        </is>
-      </c>
-      <c r="E63" s="72" t="inlineStr"/>
+      <c r="E63" s="71" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5348,8 +5461,8 @@
           <t>Капитализация, $ млн</t>
         </is>
       </c>
-      <c r="C64" s="71" t="n">
-        <v>4228.799095</v>
+      <c r="C64" s="70" t="n">
+        <v>4238.049641</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5369,8 +5482,8 @@
           <t>FDV, $ млн</t>
         </is>
       </c>
-      <c r="C65" s="71" t="n">
-        <v>7895.284465</v>
+      <c r="C65" s="70" t="n">
+        <v>7912.528129</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5390,8 +5503,8 @@
           <t>TVL сейчас, $ млн</t>
         </is>
       </c>
-      <c r="C66" s="71" t="n">
-        <v>55.149255</v>
+      <c r="C66" s="70" t="n">
+        <v>54.352401</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5415,7 +5528,7 @@
           <t>TVL 6 мес назад, $ млн</t>
         </is>
       </c>
-      <c r="C67" s="71" t="n">
+      <c r="C67" s="70" t="n">
         <v>55.174661</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -5440,7 +5553,7 @@
           <t>Активные адреса/день сейчас</t>
         </is>
       </c>
-      <c r="C68" s="71" t="n">
+      <c r="C68" s="70" t="n">
         <v>103801</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -5465,7 +5578,7 @@
           <t>Активные адреса/день 6 мес назад</t>
         </is>
       </c>
-      <c r="C69" s="71" t="n">
+      <c r="C69" s="70" t="n">
         <v>69929</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -5490,7 +5603,7 @@
           <t>Доход/комиссии за год, $ млн</t>
         </is>
       </c>
-      <c r="C70" s="71" t="n">
+      <c r="C70" s="70" t="n">
         <v>2.119862</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -5505,61 +5618,67 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="72" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>TON</t>
         </is>
       </c>
-      <c r="B71" s="72" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>Активных разработчиков/мес</t>
         </is>
       </c>
-      <c r="C71" s="73" t="n"/>
-      <c r="D71" s="72" t="inlineStr">
+      <c r="C71" s="70" t="n">
+        <v>191</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Open Dev Data</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="71" t="inlineStr">
+        <is>
+          <t>TON</t>
+        </is>
+      </c>
+      <c r="B72" s="71" t="inlineStr">
+        <is>
+          <t>Разлок за 6 мес, % предложения</t>
+        </is>
+      </c>
+      <c r="C72" s="72" t="n"/>
+      <c r="D72" s="71" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
         </is>
       </c>
-      <c r="E71" s="72" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="72" t="inlineStr">
+      <c r="E72" s="71" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="71" t="inlineStr">
         <is>
           <t>TON</t>
         </is>
       </c>
-      <c r="B72" s="72" t="inlineStr">
-        <is>
-          <t>Разлок за 6 мес, % предложения</t>
-        </is>
-      </c>
-      <c r="C72" s="74" t="n"/>
-      <c r="D72" s="72" t="inlineStr">
+      <c r="B73" s="71" t="inlineStr">
+        <is>
+          <t>Инвесторы и команда, 1–5</t>
+        </is>
+      </c>
+      <c r="C73" s="73" t="n"/>
+      <c r="D73" s="71" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
         </is>
       </c>
-      <c r="E72" s="72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="72" t="inlineStr">
-        <is>
-          <t>TON</t>
-        </is>
-      </c>
-      <c r="B73" s="72" t="inlineStr">
-        <is>
-          <t>Инвесторы и команда, 1–5</t>
-        </is>
-      </c>
-      <c r="C73" s="73" t="n"/>
-      <c r="D73" s="72" t="inlineStr">
-        <is>
-          <t>нет данных — заполнить вручную</t>
-        </is>
-      </c>
-      <c r="E73" s="72" t="inlineStr"/>
+      <c r="E73" s="71" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5572,8 +5691,8 @@
           <t>Капитализация, $ млн</t>
         </is>
       </c>
-      <c r="C74" s="71" t="n">
-        <v>32174.288951</v>
+      <c r="C74" s="70" t="n">
+        <v>32097.231712</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5593,8 +5712,8 @@
           <t>FDV, $ млн</t>
         </is>
       </c>
-      <c r="C75" s="71" t="n">
-        <v>32174.313939</v>
+      <c r="C75" s="70" t="n">
+        <v>32097.240025</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5614,8 +5733,8 @@
           <t>TVL сейчас, $ млн</t>
         </is>
       </c>
-      <c r="C76" s="71" t="n">
-        <v>5678.20312</v>
+      <c r="C76" s="70" t="n">
+        <v>5638.408003</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5639,7 +5758,7 @@
           <t>TVL 6 мес назад, $ млн</t>
         </is>
       </c>
-      <c r="C77" s="71" t="n">
+      <c r="C77" s="70" t="n">
         <v>4797.537404</v>
       </c>
       <c r="D77" t="inlineStr">
@@ -5664,7 +5783,7 @@
           <t>Активные адреса/день сейчас</t>
         </is>
       </c>
-      <c r="C78" s="71" t="n">
+      <c r="C78" s="70" t="n">
         <v>3390556</v>
       </c>
       <c r="D78" t="inlineStr">
@@ -5689,7 +5808,7 @@
           <t>Активные адреса/день 6 мес назад</t>
         </is>
       </c>
-      <c r="C79" s="71" t="n">
+      <c r="C79" s="70" t="n">
         <v>2916537</v>
       </c>
       <c r="D79" t="inlineStr">
@@ -5714,7 +5833,7 @@
           <t>Доход/комиссии за год, $ млн</t>
         </is>
       </c>
-      <c r="C80" s="71" t="n">
+      <c r="C80" s="70" t="n">
         <v>348.971536</v>
       </c>
       <c r="D80" t="inlineStr">
@@ -5729,61 +5848,67 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="72" t="inlineStr">
+      <c r="A81" t="inlineStr">
         <is>
           <t>Tron</t>
         </is>
       </c>
-      <c r="B81" s="72" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>Активных разработчиков/мес</t>
         </is>
       </c>
-      <c r="C81" s="73" t="n"/>
-      <c r="D81" s="72" t="inlineStr">
+      <c r="C81" s="70" t="n">
+        <v>70</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Open Dev Data</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="71" t="inlineStr">
+        <is>
+          <t>Tron</t>
+        </is>
+      </c>
+      <c r="B82" s="71" t="inlineStr">
+        <is>
+          <t>Разлок за 6 мес, % предложения</t>
+        </is>
+      </c>
+      <c r="C82" s="72" t="n"/>
+      <c r="D82" s="71" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
         </is>
       </c>
-      <c r="E81" s="72" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="72" t="inlineStr">
+      <c r="E82" s="71" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="71" t="inlineStr">
         <is>
           <t>Tron</t>
         </is>
       </c>
-      <c r="B82" s="72" t="inlineStr">
-        <is>
-          <t>Разлок за 6 мес, % предложения</t>
-        </is>
-      </c>
-      <c r="C82" s="74" t="n"/>
-      <c r="D82" s="72" t="inlineStr">
+      <c r="B83" s="71" t="inlineStr">
+        <is>
+          <t>Инвесторы и команда, 1–5</t>
+        </is>
+      </c>
+      <c r="C83" s="73" t="n"/>
+      <c r="D83" s="71" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
         </is>
       </c>
-      <c r="E82" s="72" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="72" t="inlineStr">
-        <is>
-          <t>Tron</t>
-        </is>
-      </c>
-      <c r="B83" s="72" t="inlineStr">
-        <is>
-          <t>Инвесторы и команда, 1–5</t>
-        </is>
-      </c>
-      <c r="C83" s="73" t="n"/>
-      <c r="D83" s="72" t="inlineStr">
-        <is>
-          <t>нет данных — заполнить вручную</t>
-        </is>
-      </c>
-      <c r="E83" s="72" t="inlineStr"/>
+      <c r="E83" s="71" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5796,8 +5921,8 @@
           <t>Капитализация, $ млн</t>
         </is>
       </c>
-      <c r="C84" s="71" t="n">
-        <v>19075.239849</v>
+      <c r="C84" s="70" t="n">
+        <v>19786.883821</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5817,8 +5942,8 @@
           <t>FDV, $ млн</t>
         </is>
       </c>
-      <c r="C85" s="71" t="n">
-        <v>81919.814663</v>
+      <c r="C85" s="70" t="n">
+        <v>84976.014364</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5838,8 +5963,8 @@
           <t>TVL сейчас, $ млн</t>
         </is>
       </c>
-      <c r="C86" s="71" t="n">
-        <v>1190.593415</v>
+      <c r="C86" s="70" t="n">
+        <v>1171.952848</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5863,7 +5988,7 @@
           <t>TVL 6 мес назад, $ млн</t>
         </is>
       </c>
-      <c r="C87" s="71" t="n">
+      <c r="C87" s="70" t="n">
         <v>1672.171573</v>
       </c>
       <c r="D87" t="inlineStr">
@@ -5888,7 +6013,7 @@
           <t>Активные адреса/день сейчас</t>
         </is>
       </c>
-      <c r="C88" s="71" t="n">
+      <c r="C88" s="70" t="n">
         <v>86570</v>
       </c>
       <c r="D88" t="inlineStr">
@@ -5913,7 +6038,7 @@
           <t>Активные адреса/день 6 мес назад</t>
         </is>
       </c>
-      <c r="C89" s="71" t="n">
+      <c r="C89" s="70" t="n">
         <v>64504</v>
       </c>
       <c r="D89" t="inlineStr">
@@ -5938,7 +6063,7 @@
           <t>Доход/комиссии за год, $ млн</t>
         </is>
       </c>
-      <c r="C90" s="71" t="n">
+      <c r="C90" s="70" t="n">
         <v>910.588444</v>
       </c>
       <c r="D90" t="inlineStr">
@@ -5953,61 +6078,67 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="72" t="inlineStr">
+      <c r="A91" s="74" t="inlineStr">
         <is>
           <t>Hyperliquid</t>
         </is>
       </c>
-      <c r="B91" s="72" t="inlineStr">
+      <c r="B91" s="74" t="inlineStr">
         <is>
           <t>Активных разработчиков/мес</t>
         </is>
       </c>
-      <c r="C91" s="73" t="n"/>
-      <c r="D91" s="72" t="inlineStr">
+      <c r="C91" s="75" t="n">
+        <v>4</v>
+      </c>
+      <c r="D91" s="74" t="inlineStr">
+        <is>
+          <t>Open Dev Data</t>
+        </is>
+      </c>
+      <c r="E91" s="74" t="inlineStr">
+        <is>
+          <t>exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0. ⚠ за 6 мес 24 → 4: скачок больше чем в 5 раз, часто это перепривязка общих репозиториев к сети, а не реальный приток разработчиков</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="71" t="inlineStr">
+        <is>
+          <t>Hyperliquid</t>
+        </is>
+      </c>
+      <c r="B92" s="71" t="inlineStr">
+        <is>
+          <t>Разлок за 6 мес, % предложения</t>
+        </is>
+      </c>
+      <c r="C92" s="72" t="n"/>
+      <c r="D92" s="71" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
         </is>
       </c>
-      <c r="E91" s="72" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="72" t="inlineStr">
+      <c r="E92" s="71" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="71" t="inlineStr">
         <is>
           <t>Hyperliquid</t>
         </is>
       </c>
-      <c r="B92" s="72" t="inlineStr">
-        <is>
-          <t>Разлок за 6 мес, % предложения</t>
-        </is>
-      </c>
-      <c r="C92" s="74" t="n"/>
-      <c r="D92" s="72" t="inlineStr">
+      <c r="B93" s="71" t="inlineStr">
+        <is>
+          <t>Инвесторы и команда, 1–5</t>
+        </is>
+      </c>
+      <c r="C93" s="73" t="n"/>
+      <c r="D93" s="71" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
         </is>
       </c>
-      <c r="E92" s="72" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="72" t="inlineStr">
-        <is>
-          <t>Hyperliquid</t>
-        </is>
-      </c>
-      <c r="B93" s="72" t="inlineStr">
-        <is>
-          <t>Инвесторы и команда, 1–5</t>
-        </is>
-      </c>
-      <c r="C93" s="73" t="n"/>
-      <c r="D93" s="72" t="inlineStr">
-        <is>
-          <t>нет данных — заполнить вручную</t>
-        </is>
-      </c>
-      <c r="E93" s="72" t="inlineStr"/>
+      <c r="E93" s="71" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6020,8 +6151,8 @@
           <t>Капитализация, $ млн</t>
         </is>
       </c>
-      <c r="C94" s="71" t="n">
-        <v>328.245041</v>
+      <c r="C94" s="70" t="n">
+        <v>331.544745</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6041,8 +6172,8 @@
           <t>FDV, $ млн</t>
         </is>
       </c>
-      <c r="C95" s="71" t="n">
-        <v>2794.774601</v>
+      <c r="C95" s="70" t="n">
+        <v>2822.869252</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6062,8 +6193,8 @@
           <t>TVL сейчас, $ млн</t>
         </is>
       </c>
-      <c r="C96" s="71" t="n">
-        <v>1052.269901</v>
+      <c r="C96" s="70" t="n">
+        <v>1052.427495</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6087,7 +6218,7 @@
           <t>TVL 6 мес назад, $ млн</t>
         </is>
       </c>
-      <c r="C97" s="71" t="n">
+      <c r="C97" s="70" t="n">
         <v>351.735124</v>
       </c>
       <c r="D97" t="inlineStr">
@@ -6112,7 +6243,7 @@
           <t>Активные адреса/день сейчас</t>
         </is>
       </c>
-      <c r="C98" s="71" t="n">
+      <c r="C98" s="70" t="n">
         <v>19904</v>
       </c>
       <c r="D98" t="inlineStr">
@@ -6137,7 +6268,7 @@
           <t>Активные адреса/день 6 мес назад</t>
         </is>
       </c>
-      <c r="C99" s="71" t="n">
+      <c r="C99" s="70" t="n">
         <v>13399</v>
       </c>
       <c r="D99" t="inlineStr">
@@ -6162,7 +6293,7 @@
           <t>Доход/комиссии за год, $ млн</t>
         </is>
       </c>
-      <c r="C100" s="71" t="n">
+      <c r="C100" s="70" t="n">
         <v>2.102234</v>
       </c>
       <c r="D100" t="inlineStr">
@@ -6177,61 +6308,67 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="72" t="inlineStr">
+      <c r="A101" t="inlineStr">
         <is>
           <t>Monad</t>
         </is>
       </c>
-      <c r="B101" s="72" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>Активных разработчиков/мес</t>
         </is>
       </c>
-      <c r="C101" s="73" t="n"/>
-      <c r="D101" s="72" t="inlineStr">
+      <c r="C101" s="70" t="n">
+        <v>75</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Open Dev Data</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>exclusive_devs за 28 дн до 2026-09-22. Source: Open Dev Data (opendevdata.org), CC BY 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="71" t="inlineStr">
+        <is>
+          <t>Monad</t>
+        </is>
+      </c>
+      <c r="B102" s="71" t="inlineStr">
+        <is>
+          <t>Разлок за 6 мес, % предложения</t>
+        </is>
+      </c>
+      <c r="C102" s="72" t="n"/>
+      <c r="D102" s="71" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
         </is>
       </c>
-      <c r="E101" s="72" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="72" t="inlineStr">
+      <c r="E102" s="71" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="71" t="inlineStr">
         <is>
           <t>Monad</t>
         </is>
       </c>
-      <c r="B102" s="72" t="inlineStr">
-        <is>
-          <t>Разлок за 6 мес, % предложения</t>
-        </is>
-      </c>
-      <c r="C102" s="74" t="n"/>
-      <c r="D102" s="72" t="inlineStr">
+      <c r="B103" s="71" t="inlineStr">
+        <is>
+          <t>Инвесторы и команда, 1–5</t>
+        </is>
+      </c>
+      <c r="C103" s="73" t="n"/>
+      <c r="D103" s="71" t="inlineStr">
         <is>
           <t>нет данных — заполнить вручную</t>
         </is>
       </c>
-      <c r="E102" s="72" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="72" t="inlineStr">
-        <is>
-          <t>Monad</t>
-        </is>
-      </c>
-      <c r="B103" s="72" t="inlineStr">
-        <is>
-          <t>Инвесторы и команда, 1–5</t>
-        </is>
-      </c>
-      <c r="C103" s="73" t="n"/>
-      <c r="D103" s="72" t="inlineStr">
-        <is>
-          <t>нет данных — заполнить вручную</t>
-        </is>
-      </c>
-      <c r="E103" s="72" t="inlineStr"/>
+      <c r="E103" s="71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
